--- a/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
+++ b/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -141,6 +141,11 @@
       <color rgb="00000000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -218,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -290,6 +295,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -786,7 +794,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -1062,7 +1070,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1128,7 +1136,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1194,7 +1202,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1260,7 +1268,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1326,7 +1334,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1462,7 +1470,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1528,7 +1536,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1664,7 +1672,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1730,7 +1738,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1791,23 +1799,19 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>33248700</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>26578</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1816,12 +1820,12 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -1831,7 +1835,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1870,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1932,7 +1936,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -2068,7 +2072,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2134,7 +2138,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2270,7 +2274,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2336,7 +2340,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2402,7 +2406,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2468,7 +2472,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2534,7 +2538,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2600,7 +2604,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2666,7 +2670,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2732,7 +2736,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2798,7 +2802,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2864,7 +2868,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2930,7 +2934,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -3066,7 +3070,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3132,7 +3136,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3198,7 +3202,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3264,7 +3268,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3330,7 +3334,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3387,7 +3391,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1251</v>
+        <v>1186</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3396,14 +3400,14 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
         <v>28147500</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>22500</v>
+        <v>23733</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3462,7 +3466,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3528,7 +3532,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3664,7 +3668,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3730,7 +3734,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3866,7 +3870,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3932,7 +3936,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -4068,7 +4072,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4134,7 +4138,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4270,7 +4274,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4336,7 +4340,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4402,7 +4406,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4468,7 +4472,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4534,7 +4538,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2025-02-16</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4600,7 +4604,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4666,7 +4670,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4732,7 +4736,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4798,7 +4802,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4864,7 +4868,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4930,7 +4934,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2020-06-18</t>
+          <t>2020-06-19</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4996,7 +5000,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -5062,7 +5066,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -5128,7 +5132,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5264,7 +5268,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5330,7 +5334,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5396,7 +5400,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5462,7 +5466,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5528,7 +5532,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5594,7 +5598,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5660,7 +5664,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5726,7 +5730,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5792,7 +5796,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5858,7 +5862,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5924,7 +5928,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5990,7 +5994,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2023-11-30</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -6056,7 +6060,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -6122,7 +6126,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -6188,7 +6192,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -6254,7 +6258,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6320,7 +6324,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-11-30</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6386,7 +6390,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6452,7 +6456,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6518,7 +6522,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6584,7 +6588,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6650,7 +6654,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6716,7 +6720,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2023-12-11</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6782,7 +6786,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2023-10-30</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6848,7 +6852,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6914,7 +6918,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6980,7 +6984,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -7046,7 +7050,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -7112,7 +7116,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -7178,7 +7182,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -7244,7 +7248,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -7310,7 +7314,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7376,7 +7380,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-11-30</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7442,7 +7446,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7508,7 +7512,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7574,7 +7578,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7640,7 +7644,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7706,7 +7710,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7772,7 +7776,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2020-05-17</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7838,7 +7842,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7974,7 +7978,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -8040,7 +8044,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -8106,7 +8110,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2023-10-30</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -8172,7 +8176,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2023-12-07</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -8238,7 +8242,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -8304,7 +8308,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2020-05-27</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -8370,7 +8374,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8436,7 +8440,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8502,7 +8506,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2020-05-17</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8568,7 +8572,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8634,7 +8638,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8700,7 +8704,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2020-05-14</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8766,7 +8770,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2019-12-11</t>
+          <t>2019-12-12</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8832,7 +8836,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8898,7 +8902,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2020-05-14</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8964,7 +8968,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2020-05-25</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -9030,7 +9034,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -9096,7 +9100,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2020-05-17</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -9162,7 +9166,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2020-05-17</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -9228,7 +9232,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -9294,7 +9298,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2020-05-27</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -9360,7 +9364,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2020-05-19</t>
+          <t>2020-05-20</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -9426,7 +9430,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -9492,7 +9496,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2020-12-23</t>
+          <t>2020-12-24</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9558,7 +9562,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2021-03-31</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9624,7 +9628,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9690,7 +9694,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9756,7 +9760,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9822,7 +9826,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9888,7 +9892,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9954,7 +9958,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -10020,7 +10024,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -10086,7 +10090,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -10152,7 +10156,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -10218,7 +10222,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -10284,7 +10288,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -10350,7 +10354,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -10416,7 +10420,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -10482,7 +10486,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -10548,7 +10552,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -10614,7 +10618,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10680,7 +10684,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10746,7 +10750,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10812,7 +10816,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10878,7 +10882,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10944,7 +10948,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -11010,7 +11014,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -11076,7 +11080,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -11142,7 +11146,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -11208,7 +11212,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -11274,7 +11278,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -11340,7 +11344,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -11406,7 +11410,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -11472,7 +11476,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -11538,7 +11542,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -11604,7 +11608,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11670,7 +11674,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11736,7 +11740,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11802,7 +11806,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11868,7 +11872,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11934,7 +11938,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -12000,7 +12004,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -12066,7 +12070,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -12132,7 +12136,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -12198,7 +12202,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -12264,7 +12268,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -12330,7 +12334,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -12396,7 +12400,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -12462,7 +12466,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -12528,7 +12532,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -12594,7 +12598,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -12660,7 +12664,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12726,7 +12730,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12792,7 +12796,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12858,7 +12862,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12924,7 +12928,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12990,7 +12994,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -13056,7 +13060,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -13122,7 +13126,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -13188,7 +13192,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -13254,7 +13258,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -13320,7 +13324,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -13386,7 +13390,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -13452,7 +13456,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -13518,7 +13522,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -13584,7 +13588,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -13650,7 +13654,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -13716,7 +13720,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -13782,7 +13786,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13848,7 +13852,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13914,7 +13918,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13980,7 +13984,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -14046,7 +14050,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2020-07-21</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -14112,7 +14116,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -14178,7 +14182,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -14244,7 +14248,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2020-05-19</t>
+          <t>2020-05-20</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -14310,7 +14314,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2020-05-31</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -14376,7 +14380,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -14442,7 +14446,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2020-06-11</t>
+          <t>2020-06-12</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -14508,7 +14512,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -14574,7 +14578,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -14640,7 +14644,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -14706,7 +14710,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -14772,7 +14776,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -14838,7 +14842,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14904,7 +14908,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14970,7 +14974,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -15036,7 +15040,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -15102,7 +15106,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -15168,7 +15172,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -15234,7 +15238,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -15300,7 +15304,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -15366,7 +15370,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -15432,7 +15436,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -15498,7 +15502,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -15564,7 +15568,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -15630,7 +15634,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -15696,7 +15700,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -15762,7 +15766,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -16033,7 +16037,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -16043,12 +16047,12 @@
       </c>
       <c r="H233" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I233" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J233" s="3" t="inlineStr">
@@ -16058,12 +16062,12 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L233" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M233" s="3" t="inlineStr">
@@ -16073,7 +16077,7 @@
       </c>
       <c r="N233" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -16103,7 +16107,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -16113,12 +16117,12 @@
       </c>
       <c r="H234" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I234" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J234" s="3" t="inlineStr">
@@ -16128,12 +16132,12 @@
       </c>
       <c r="K234" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L234" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M234" s="3" t="inlineStr">
@@ -16143,7 +16147,7 @@
       </c>
       <c r="N234" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -16598,7 +16602,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -16664,7 +16668,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -16870,7 +16874,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -16927,7 +16931,7 @@
         </is>
       </c>
       <c r="E246" s="4" t="n">
-        <v>890</v>
+        <v>813</v>
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
@@ -16936,14 +16940,14 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
         <v>20309800</v>
       </c>
       <c r="I246" s="5" t="n">
-        <v>22820</v>
+        <v>24981</v>
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
@@ -17142,7 +17146,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -17208,7 +17212,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -17414,7 +17418,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -17480,7 +17484,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -17686,7 +17690,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -17752,7 +17756,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -17958,7 +17962,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -18024,7 +18028,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -18230,7 +18234,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -18296,7 +18300,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -18502,7 +18506,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -18568,7 +18572,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -18774,7 +18778,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -18840,7 +18844,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -19046,7 +19050,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -19112,7 +19116,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -19318,7 +19322,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -19384,7 +19388,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -19585,7 +19589,7 @@
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -19595,12 +19599,12 @@
       </c>
       <c r="H285" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I285" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J285" s="3" t="inlineStr">
@@ -19610,12 +19614,12 @@
       </c>
       <c r="K285" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L285" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M285" s="3" t="inlineStr">
@@ -19625,7 +19629,7 @@
       </c>
       <c r="N285" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19660,7 +19664,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -20146,7 +20150,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -20212,7 +20216,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -20278,7 +20282,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -20344,7 +20348,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -20410,7 +20414,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -20476,7 +20480,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -20542,7 +20546,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -20608,7 +20612,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -20674,7 +20678,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -20740,7 +20744,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2023-12-11</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -20806,7 +20810,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -20872,7 +20876,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -20938,7 +20942,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -21004,7 +21008,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2023-11-21</t>
+          <t>2023-11-22</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -21070,7 +21074,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -21136,7 +21140,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -21202,7 +21206,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -21268,7 +21272,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -21334,7 +21338,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -21400,7 +21404,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -21466,7 +21470,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -21532,7 +21536,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -21598,7 +21602,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -21664,7 +21668,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -21730,7 +21734,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -21796,7 +21800,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -21862,7 +21866,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -21928,7 +21932,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -21994,7 +21998,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -22060,7 +22064,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -22126,7 +22130,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -22192,7 +22196,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -22258,7 +22262,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -22324,7 +22328,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -22390,7 +22394,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -22456,7 +22460,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -22522,7 +22526,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -22588,7 +22592,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -22654,7 +22658,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -22720,7 +22724,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -22786,7 +22790,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2023-12-07</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -22852,7 +22856,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -22918,7 +22922,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -22984,7 +22988,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -23050,7 +23054,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2023-12-07</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -23116,7 +23120,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2023-12-11</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -23182,7 +23186,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -23248,7 +23252,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -23314,7 +23318,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2023-10-30</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -23380,7 +23384,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -23446,7 +23450,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2023-12-03</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -23512,7 +23516,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -23578,7 +23582,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2023-12-03</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -23644,7 +23648,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -23710,7 +23714,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -23776,7 +23780,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -23842,7 +23846,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -23908,7 +23912,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -23974,7 +23978,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -24040,7 +24044,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -24106,7 +24110,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -24172,7 +24176,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -24238,7 +24242,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -24304,7 +24308,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -24440,7 +24444,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -24506,7 +24510,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -24572,7 +24576,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -24638,7 +24642,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -24704,7 +24708,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -24770,7 +24774,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -24836,7 +24840,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -24902,7 +24906,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -24968,7 +24972,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -25034,7 +25038,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -25100,7 +25104,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -25306,7 +25310,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -25372,7 +25376,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -25438,7 +25442,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -25504,7 +25508,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -25640,7 +25644,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -25706,7 +25710,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -25842,7 +25846,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -25908,7 +25912,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -26044,7 +26048,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -26110,7 +26114,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -26176,7 +26180,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -26242,7 +26246,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -26308,7 +26312,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -26374,7 +26378,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -26440,7 +26444,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -26506,7 +26510,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -26572,7 +26576,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -26638,7 +26642,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -26704,7 +26708,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -26840,7 +26844,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -26906,7 +26910,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -27042,7 +27046,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -27108,7 +27112,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -27244,7 +27248,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -27310,7 +27314,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -27556,7 +27560,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27566,7 +27570,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27615,7 +27619,7 @@
           <t>C | 2357呎 (4+房)
 $7787万
 $33,037/呎
-(25年-11月-18日)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
     </row>
@@ -27671,7 +27675,7 @@
           <t>A | 2669呎 (4+房)
 $7877万
 $29,514/呎
-(25年-03月-12日)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr"/>
@@ -27680,7 +27684,7 @@
           <t>C | 1186呎 (3房)
 $3125万
 $26,347/呎
-(26年-01月-18日)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
     </row>
@@ -27695,7 +27699,7 @@
           <t>A | 1367呎 (3房)
 $3612万
 $26,426/呎
-(24年-07月-25日)</t>
+(24年-07月-26日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -27703,7 +27707,7 @@
           <t>B | 1368呎 (3房)
 $3618万
 $26,444/呎
-(24年-07月-25日)</t>
+(24年-07月-26日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -27711,7 +27715,7 @@
           <t>C | 1186呎 (3房)
 $3002万
 $25,315/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -27726,7 +27730,7 @@
           <t>A | 1367呎 (3房)
 $3500万
 $25,604/呎
-(24年-10月-09日)</t>
+(24年-10月-10日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -27734,7 +27738,7 @@
           <t>B | 1368呎 (3房)
 $3473万
 $25,386/呎
-(24年-12月-23日)</t>
+(24年-12月-24日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -27757,7 +27761,7 @@
           <t>A | 1367呎 (3房)
 $3454万
 $25,264/呎
-(25年-03月-02日)</t>
+(25年-03月-03日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -27765,7 +27769,7 @@
           <t>B | 1368呎 (3房)
 $3429万
 $25,069/呎
-(25年-03月-02日)</t>
+(25年-03月-03日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -27788,7 +27792,7 @@
           <t>A | 1367呎 (3房)
 $3432万
 $25,105/呎
-(24年-12月-15日)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -27796,10 +27800,72 @@
           <t>B | 1368呎 (3房)
 $3742万
 $27,350/呎
-(25年-03月-13日)</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
+(25年-03月-14日)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+$3325万
+$26,578/呎
+(26年-07月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3425万
+$25,052/呎
+(24年-12月-06日)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3734万
+$27,297/呎
+(25年-03月-14日)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3417万
+$24,999/呎
+(24年-12月-16日)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3727万
+$27,244/呎
+(25年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 招标单位
@@ -27808,29 +27874,215 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3425万
-$25,052/呎
-(24年-12月-05日)</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
+$3417万
+$24,999/呎
+(24年-12月-10日)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3734万
-$27,297/呎
-(25年-03月-13日)</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
+$3340万
+$24,415/呎
+(25年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2753万
+$23,210/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3396万
+$24,841/呎
+(24年-11月-21日)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3321万
+$24,275/呎
+(25年-07月-22日)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2852万
+$24,050/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3403万
+$24,894/呎
+(24年-12月-24日)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3313万
+$24,218/呎
+(25年-06月-13日)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2830万
+$23,860/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$4198万
+$30,710/呎
+(26年-02月-10日)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3270万
+$23,905/呎
+(25年-08月-07日)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3374万
+$24,682/呎
+(25年-01月-03日)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3227万
+$23,588/呎
+(24年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2792万
+$23,543/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3665万
+$26,811/呎
+(25年-06月-13日)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3270万
+$23,905/呎
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2815万
+$23,733/呎
+(26年-07月-28日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3338万
+$24,418/呎
+(25年-11月-20日)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3205万
+$23,429/呎
+(25年-08月-15日)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -27839,29 +28091,29 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3417万
-$24,999/呎
-(24年-12月-15日)</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
+$3330万
+$24,360/呎
+(25年-11月-19日)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3727万
-$27,244/呎
-(25年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
+$3212万
+$23,482/呎
+(26年-03月-30日)</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 招标单位
@@ -27870,122 +28122,29 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3417万
-$24,999/呎
-(24年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
+$3352万
+$24,524/呎
+(25年-12月-17日)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3340万
-$24,415/呎
-(25年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2753万
-$23,210/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3396万
-$24,841/呎
-(24年-11月-20日)</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3321万
-$24,275/呎
-(25年-07月-21日)</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2852万
-$24,050/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3403万
-$24,894/呎
-(24年-12月-23日)</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3313万
-$24,218/呎
-(25年-06月-12日)</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2830万
-$23,860/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$4198万
-$30,710/呎
-(26年-02月-09日)</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3270万
-$23,905/呎
-(25年-08月-06日)</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
+$3209万
+$23,461/呎
+(26年-04月-13日)</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 招标单位
@@ -27994,91 +28153,29 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3374万
-$24,682/呎
-(25年-01月-02日)</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
+$3324万
+$24,312/呎
+(24年-04月-12日)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3227万
-$23,588/呎
-(24年-08月-22日)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2792万
-$23,543/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3665万
-$26,811/呎
-(25年-06月-12日)</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3270万
-$23,905/呎
-(26年-04月-19日)</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-$2815万
-$22,500/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3338万
-$24,418/呎
-(25年-11月-19日)</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3205万
-$23,429/呎
-(25年-08月-14日)</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
+$3193万
+$23,342/呎
+(24年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -28087,99 +28184,6 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3330万
-$24,360/呎
-(25年-11月-18日)</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3212万
-$23,482/呎
-(26年-03月-29日)</t>
-        </is>
-      </c>
-      <c r="D22" s="23" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3352万
-$24,524/呎
-(25年-12月-16日)</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3209万
-$23,461/呎
-(26年-04月-12日)</t>
-        </is>
-      </c>
-      <c r="D23" s="23" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3324万
-$24,312/呎
-(24年-04月-11日)</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3193万
-$23,342/呎
-(24年-04月-07日)</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
         <is>
@@ -28191,7 +28195,7 @@
           <t>A | 1367呎 (3房)
 $3604万
 $26,364/呎
-(25年-02月-16日)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -28199,7 +28203,7 @@
           <t>B | 1368呎 (3房)
 $3180万
 $23,246/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -28207,7 +28211,7 @@
           <t>C | 1251呎 (3房)
 $2690万
 $21,500/呎
-(26年-07月-19日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
     </row>
@@ -28222,7 +28226,7 @@
           <t>A | 1367呎 (3房)
 $3652万
 $26,719/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -28230,7 +28234,7 @@
           <t>B | 1368呎 (3房)
 $3154万
 $23,059/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -28238,7 +28242,7 @@
           <t>C | 1186呎 (3房)
 $2555万
 $21,539/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -28253,7 +28257,7 @@
           <t>A | 1445呎 (3房)
 $4494万
 $31,100/呎
-(20年-06月-18日)</t>
+(20年-06月-19日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -28261,7 +28265,7 @@
           <t>B | 1368呎 (3房)
 $3133万
 $22,901/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -28269,7 +28273,7 @@
           <t>C | 1186呎 (3房)
 $2540万
 $21,413/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -28284,7 +28288,7 @@
           <t>A | 1367呎 (3房)
 $3100万
 $22,677/呎
-(24年-04月-08日)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -28292,7 +28296,7 @@
           <t>B | 1352呎 (3房)
 $3032万
 $22,423/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -28300,7 +28304,7 @@
           <t>C | 1186呎 (3房)
 $2527万
 $21,307/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
     </row>
@@ -28315,7 +28319,7 @@
           <t>A | 2626呎 (4+房)
 $6828万
 $26,000/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr"/>
@@ -28457,7 +28461,7 @@
           <t>B | 3461呎 (4+房)
 $12067万
 $34,864/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -28465,7 +28469,7 @@
           <t>C | 2334呎 (4+房)
 $7700万
 $32,991/呎
-(24年-04月-14日)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -28480,7 +28484,7 @@
           <t>A | 2338呎 (4+房)
 $7600万
 $32,506/呎
-(24年-04月-08日)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr"/>
@@ -28498,7 +28502,7 @@
           <t>B | 1351呎 (3房)
 $3630万
 $26,866/呎
-(24年-04月-23日)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -28506,7 +28510,7 @@
           <t>C | 1180呎 (3房)
 $2612万
 $22,139/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
     </row>
@@ -28521,7 +28525,7 @@
           <t>A | 1325呎 (3房)
 $3493万
 $26,366/呎
-(24年-01月-24日)</t>
+(24年-01月-25日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -28529,7 +28533,7 @@
           <t>B | 1347呎 (3房)
 $3548万
 $26,342/呎
-(24年-01月-25日)</t>
+(24年-01月-26日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -28537,7 +28541,7 @@
           <t>C | 1180呎 (3房)
 $2662万
 $22,561/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -28552,7 +28556,7 @@
           <t>A | 1325呎 (3房)
 $3479万
 $26,260/呎
-(23年-11月-30日)</t>
+(23年-12月-01日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -28560,7 +28564,7 @@
           <t>B | 1347呎 (3房)
 $3491万
 $25,919/呎
-(23年-10月-16日)</t>
+(23年-10月-17日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -28568,7 +28572,7 @@
           <t>C | 1180呎 (3房)
 $2700万
 $22,881/呎
-(24年-09月-16日)</t>
+(24年-09月-17日)</t>
         </is>
       </c>
     </row>
@@ -28583,7 +28587,7 @@
           <t>A | 1403呎 (3房)
 $3115万
 $22,200/呎
-(23年-10月-17日)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -28591,7 +28595,7 @@
           <t>B | 1425呎 (3房)
 $3164万
 $22,200/呎
-(23年-10月-18日)</t>
+(23年-10月-19日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -28599,7 +28603,7 @@
           <t>C | 1180呎 (3房)
 $2612万
 $22,139/呎
-(24年-08月-22日)</t>
+(24年-08月-23日)</t>
         </is>
       </c>
     </row>
@@ -28614,7 +28618,7 @@
           <t>A | 1325呎 (3房)
 $3227万
 $24,354/呎
-(24年-02月-05日)</t>
+(24年-02月-06日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -28622,7 +28626,7 @@
           <t>B | 1347呎 (3房)
 $3349万
 $24,861/呎
-(23年-11月-29日)</t>
+(23年-11月-30日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -28630,7 +28634,7 @@
           <t>C | 1180呎 (3房)
 $2995万
 $25,380/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
     </row>
@@ -28645,7 +28649,7 @@
           <t>A | 1403呎 (3房)
 $3073万
 $21,900/呎
-(23年-10月-16日)</t>
+(23年-10月-17日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -28653,7 +28657,7 @@
           <t>B | 1425呎 (3房)
 $3121万
 $21,900/呎
-(23年-10月-23日)</t>
+(23年-10月-24日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -28661,7 +28665,7 @@
           <t>C | 1180呎 (3房)
 $2749万
 $23,299/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
     </row>
@@ -28676,7 +28680,7 @@
           <t>A | 1403呎 (3房)
 $3087万
 $22,000/呎
-(23年-10月-30日)</t>
+(23年-10月-31日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -28684,7 +28688,7 @@
           <t>B | 1347呎 (3房)
 $3206万
 $23,803/呎
-(23年-12月-11日)</t>
+(23年-12月-12日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -28692,7 +28696,7 @@
           <t>C | 1180呎 (3房)
 $3084万
 $26,139/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -28707,7 +28711,7 @@
           <t>A | 1403呎 (3房)
 $3146万
 $22,420/呎
-(23年-11月-13日)</t>
+(23年-11月-14日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -28715,7 +28719,7 @@
           <t>B | 1425呎 (3房)
 $3120万
 $21,896/呎
-(23年-10月-18日)</t>
+(23年-10月-19日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -28723,7 +28727,7 @@
           <t>C | 1180呎 (3房)
 $2608万
 $22,099/呎
-(24年-04月-16日)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -28738,7 +28742,7 @@
           <t>A | 1403呎 (3房)
 $3199万
 $22,800/呎
-(23年-10月-17日)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -28746,7 +28750,7 @@
           <t>B | 1347呎 (3房)
 $3164万
 $23,486/呎
-(24年-01月-02日)</t>
+(24年-01月-03日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -28754,7 +28758,7 @@
           <t>C | 1180呎 (3房)
 $2692万
 $22,814/呎
-(26年-06月-23日)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -28769,7 +28773,7 @@
           <t>A | 1325呎 (3房)
 $3115万
 $23,507/呎
-(23年-11月-29日)</t>
+(23年-11月-30日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -28777,7 +28781,7 @@
           <t>B | 1347呎 (3房)
 $3164万
 $23,486/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -28785,7 +28789,7 @@
           <t>C | 1180呎 (3房)
 $2580万
 $21,864/呎
-(24年-04月-02日)</t>
+(24年-04月-03日)</t>
         </is>
       </c>
     </row>
@@ -28800,7 +28804,7 @@
           <t>A | 1403呎 (3房)
 $3016万
 $21,500/呎
-(23年-10月-17日)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -28808,7 +28812,7 @@
           <t>B | 1425呎 (3房)
 $2878万
 $20,200/呎
-(23年-10月-12日)</t>
+(23年-10月-13日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -28816,7 +28820,7 @@
           <t>C | 1180呎 (3房)
 $2532万
 $21,454/呎
-(24年-03月-05日)</t>
+(24年-03月-06日)</t>
         </is>
       </c>
     </row>
@@ -28831,7 +28835,7 @@
           <t>A | 1403呎 (3房)
 $4378万
 $31,206/呎
-(20年-05月-17日)</t>
+(20年-05月-18日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -28839,7 +28843,7 @@
           <t>B | 1425呎 (3房)
 $2861万
 $20,080/呎
-(23年-10月-05日)</t>
+(23年-10月-06日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -28847,7 +28851,7 @@
           <t>C | 1180呎 (3房)
 $2488万
 $21,085/呎
-(24年-01月-28日)</t>
+(24年-01月-29日)</t>
         </is>
       </c>
     </row>
@@ -28862,7 +28866,7 @@
           <t>A | 1403呎 (3房)
 $2921万
 $20,820/呎
-(23年-11月-08日)</t>
+(23年-11月-09日)</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -28878,7 +28882,7 @@
           <t>C | 1244呎 (3房)
 $2513万
 $20,200/呎
-(23年-10月-18日)</t>
+(23年-10月-19日)</t>
         </is>
       </c>
     </row>
@@ -28893,7 +28897,7 @@
           <t>A | 1325呎 (3房)
 $2908万
 $21,947/呎
-(23年-12月-06日)</t>
+(23年-12月-07日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -28901,7 +28905,7 @@
           <t>B | 1425呎 (3房)
 $2850万
 $20,000/呎
-(23年-10月-30日)</t>
+(23年-10月-31日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -28909,7 +28913,7 @@
           <t>C | 1180呎 (3房)
 $2415万
 $20,464/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
     </row>
@@ -28924,7 +28928,7 @@
           <t>A | 1325呎 (3房)
 $2868万
 $21,642/呎
-(23年-12月-05日)</t>
+(23年-12月-06日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -28932,7 +28936,7 @@
           <t>B | 1425呎 (3房)
 $4225万
 $29,650/呎
-(20年-05月-27日)</t>
+(20年-05月-28日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -28940,7 +28944,7 @@
           <t>C | 1180呎 (3房)
 $2427万
 $20,570/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
     </row>
@@ -28955,7 +28959,7 @@
           <t>A | 1325呎 (3房)
 $2778万
 $20,966/呎
-(23年-10月-16日)</t>
+(23年-10月-17日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -28963,7 +28967,7 @@
           <t>B | 1347呎 (3房)
 $4185万
 $31,066/呎
-(20年-05月-17日)</t>
+(20年-05月-18日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -28971,7 +28975,7 @@
           <t>C | 1180呎 (3房)
 $2140万
 $18,133/呎
-(25年-11月-18日)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
     </row>
@@ -28986,7 +28990,7 @@
           <t>A | 1403呎 (3房)
 $4349万
 $31,000/呎
-(19年-12月-11日)</t>
+(19年-12月-12日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -28994,7 +28998,7 @@
           <t>B | 1425呎 (3房)
 $4175万
 $29,295/呎
-(20年-05月-14日)</t>
+(20年-05月-15日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -29002,7 +29006,7 @@
           <t>C | 1180呎 (3房)
 $2140万
 $18,133/呎
-(26年-01月-01日)</t>
+(26年-01月-02日)</t>
         </is>
       </c>
     </row>
@@ -29017,7 +29021,7 @@
           <t>A | 1403呎 (3房)
 $4021万
 $28,659/呎
-(20年-05月-25日)</t>
+(20年-05月-26日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -29025,7 +29029,7 @@
           <t>B | 1425呎 (3房)
 $4118万
 $28,902/呎
-(20年-05月-14日)</t>
+(20年-05月-15日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -29033,7 +29037,7 @@
           <t>C | 1180呎 (3房)
 $2132万
 $18,070/呎
-(26年-01月-25日)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
     </row>
@@ -29048,7 +29052,7 @@
           <t>A | 1325呎 (3房)
 $3934万
 $29,690/呎
-(20年-05月-17日)</t>
+(20年-05月-18日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -29056,7 +29060,7 @@
           <t>B | 1347呎 (3房)
 $4086万
 $30,332/呎
-(20年-05月-17日)</t>
+(20年-05月-18日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -29064,7 +29068,7 @@
           <t>C | 1180呎 (3房)
 $2131万
 $18,059/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
     </row>
@@ -29079,7 +29083,7 @@
           <t>A | 1403呎 (3房)
 $3931万
 $28,018/呎
-(20年-05月-19日)</t>
+(20年-05月-20日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -29087,7 +29091,7 @@
           <t>B | 1425呎 (3房)
 $4053万
 $28,445/呎
-(20年-05月-27日)</t>
+(20年-05月-28日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -29095,7 +29099,7 @@
           <t>C | 1180呎 (3房)
 $2130万
 $18,049/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -29110,7 +29114,7 @@
           <t>A | 1403呎 (3房)
 $3931万
 $28,018/呎
-(21年-03月-30日)</t>
+(21年-03月-31日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -29118,7 +29122,7 @@
           <t>B | 1425呎 (3房)
 $4041万
 $28,360/呎
-(20年-12月-23日)</t>
+(20年-12月-24日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -29126,7 +29130,7 @@
           <t>C | 1180呎 (3房)
 $2128万
 $18,038/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
     </row>
@@ -29141,7 +29145,7 @@
           <t>A | 1325呎 (3房)
 $2804万
 $21,163/呎
-(24年-01月-16日)</t>
+(24年-01月-17日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -29149,7 +29153,7 @@
           <t>B | 1330呎 (3房)
 $2800万
 $21,053/呎
-(24年-01月-18日)</t>
+(24年-01月-19日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -29157,7 +29161,7 @@
           <t>C | 1180呎 (3房)
 $2127万
 $18,027/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
     </row>
@@ -29174,7 +29178,7 @@
           <t>C | 2251呎 (4+房)
 $5853万
 $26,000/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
     </row>
@@ -29314,7 +29318,7 @@
           <t>C | 1683呎 (4+房)
 $5471万
 $32,505/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr"/>
@@ -29322,45 +29326,45 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 3255呎 (4+房)
+$11039万
+$33,915/呎
+(25年-02月-26日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 845呎 (2房)
 $1984万
 $23,479/呎
-(25年-03月-10日)</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
+(25年-03月-11日)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 845呎 (2房)
 $1873万
 $22,169/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 3255呎 (4+房)
-$11039万
-$33,915/呎
-(25年-02月-25日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
+(25年-07月-11日)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -29373,7 +29377,7 @@
           <t>A | 2065呎 (4+房)
 $6250万
 $30,266/呎
-(24年-02月-01日)</t>
+(24年-02月-02日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr"/>
@@ -29382,7 +29386,7 @@
           <t>C | 845呎 (2房)
 $1978万
 $23,411/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -29390,7 +29394,7 @@
           <t>D | 845呎 (2房)
 $1883万
 $22,280/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -29405,7 +29409,7 @@
           <t>A | 2002呎 (4+房)
 $6254万
 $31,239/呎
-(24年-03月-04日)</t>
+(24年-03月-05日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr"/>
@@ -29414,7 +29418,7 @@
           <t>C | 845呎 (2房)
 $1957万
 $23,157/呎
-(26年-02月-24日)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -29422,7 +29426,7 @@
           <t>D | 845呎 (2房)
 $1861万
 $22,025/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -29437,7 +29441,7 @@
           <t>A | 1118呎 (3房)
 $2677万
 $23,945/呎
-(26年-03月-19日)</t>
+(26年-03月-20日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -29445,7 +29449,7 @@
           <t>B | 1153呎 (3房)
 $2616万
 $22,689/呎
-(24年-10月-14日)</t>
+(24年-10月-15日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -29453,7 +29457,7 @@
           <t>C | 845呎 (2房)
 $1915万
 $22,659/呎
-(24年-08月-29日)</t>
+(24年-08月-30日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -29461,7 +29465,7 @@
           <t>D | 844呎 (2房)
 $1840万
 $21,806/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -29476,7 +29480,7 @@
           <t>A | 1118呎 (3房)
 $2650万
 $23,703/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -29484,7 +29488,7 @@
           <t>B | 1153呎 (3房)
 $2579万
 $22,368/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -29492,7 +29496,7 @@
           <t>C | 845呎 (2房)
 $1943万
 $22,991/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -29500,7 +29504,7 @@
           <t>D | 844呎 (2房)
 $1822万
 $21,584/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
     </row>
@@ -29515,7 +29519,7 @@
           <t>A | 1118呎 (3房)
 $2610万
 $23,345/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -29523,7 +29527,7 @@
           <t>B | 1153呎 (3房)
 $2558万
 $22,183/呎
-(25年-08月-24日)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -29531,7 +29535,7 @@
           <t>C | 845呎 (2房)
 $1868万
 $22,107/呎
-(25年-06月-01日)</t>
+(25年-06月-02日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -29539,7 +29543,7 @@
           <t>D | 844呎 (2房)
 $1803万
 $21,361/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
     </row>
@@ -29554,7 +29558,7 @@
           <t>A | 1118呎 (3房)
 $2892万
 $25,867/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -29562,7 +29566,7 @@
           <t>B | 1153呎 (3房)
 $2535万
 $21,987/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -29570,7 +29574,7 @@
           <t>C | 845呎 (2房)
 $1840万
 $21,775/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -29578,7 +29582,7 @@
           <t>D | 844呎 (2房)
 $1784万
 $21,139/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -29593,7 +29597,7 @@
           <t>A | 1118呎 (3房)
 $2560万
 $22,898/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -29601,7 +29605,7 @@
           <t>B | 1153呎 (3房)
 $2535万
 $21,987/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -29609,7 +29613,7 @@
           <t>C | 845呎 (2房)
 $1905万
 $22,549/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -29617,7 +29621,7 @@
           <t>D | 844呎 (2房)
 $1765万
 $20,916/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -29632,7 +29636,7 @@
           <t>A | 1118呎 (3房)
 $2542万
 $22,737/呎
-(26年-01月-04日)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -29640,7 +29644,7 @@
           <t>B | 1153呎 (3房)
 $2870万
 $24,892/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -29648,7 +29652,7 @@
           <t>C | 845呎 (2房)
 $1882万
 $22,272/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -29656,7 +29660,7 @@
           <t>D | 844呎 (2房)
 $1728万
 $20,471/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
     </row>
@@ -29671,7 +29675,7 @@
           <t>A | 1118呎 (3房)
 $2535万
 $22,674/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -29679,7 +29683,7 @@
           <t>B | 1153呎 (3房)
 $2497万
 $21,660/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -29687,7 +29691,7 @@
           <t>C | 845呎 (2房)
 $1873万
 $22,162/呎
-(26年-03月-15日)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -29695,7 +29699,7 @@
           <t>D | 844呎 (2房)
 $1765万
 $20,916/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -29710,7 +29714,7 @@
           <t>A | 1118呎 (3房)
 $2505万
 $22,407/呎
-(25年-10月-30日)</t>
+(25年-10月-31日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -29718,7 +29722,7 @@
           <t>B | 1153呎 (3房)
 $2491万
 $21,606/呎
-(25年-05月-01日)</t>
+(25年-05月-02日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -29726,7 +29730,7 @@
           <t>C | 845呎 (2房)
 $1857万
 $21,974/呎
-(26年-04月-07日)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -29734,7 +29738,7 @@
           <t>D | 844呎 (2房)
 $1708万
 $20,237/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
     </row>
@@ -29749,7 +29753,7 @@
           <t>A | 1118呎 (3房)
 $2493万
 $22,297/呎
-(25年-07月-27日)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -29757,7 +29761,7 @@
           <t>B | 1153呎 (3房)
 $2465万
 $21,379/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -29765,7 +29769,7 @@
           <t>C | 845呎 (2房)
 $1840万
 $21,775/呎
-(26年-01月-15日)</t>
+(26年-01月-16日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -29773,7 +29777,7 @@
           <t>D | 844呎 (2房)
 $1694万
 $20,071/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
     </row>
@@ -29788,7 +29792,7 @@
           <t>A | 1118呎 (3房)
 $2473万
 $22,122/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -29796,7 +29800,7 @@
           <t>B | 1153呎 (3房)
 $2450万
 $21,249/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -29804,7 +29808,7 @@
           <t>C | 845呎 (2房)
 $1831万
 $21,664/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -29812,7 +29816,7 @@
           <t>D | 844呎 (2房)
 $1690万
 $20,026/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
     </row>
@@ -29827,7 +29831,7 @@
           <t>A | 1118呎 (3房)
 $2456万
 $21,968/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -29835,7 +29839,7 @@
           <t>B | 1153呎 (3房)
 $2426万
 $21,040/呎
-(25年-11月-02日)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -29843,7 +29847,7 @@
           <t>C | 845呎 (2房)
 $1812万
 $21,443/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -29851,7 +29855,7 @@
           <t>D | 844呎 (2房)
 $1662万
 $19,692/呎
-(25年-02月-20日)</t>
+(25年-02月-21日)</t>
         </is>
       </c>
     </row>
@@ -29866,7 +29870,7 @@
           <t>A | 1228呎 (3房)
 $3616万
 $29,450/呎
-(20年-07月-27日)</t>
+(20年-07月-28日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -29874,7 +29878,7 @@
           <t>B | 1153呎 (3房)
 $2428万
 $21,062/呎
-(26年-01月-07日)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -29882,7 +29886,7 @@
           <t>C | 845呎 (2房)
 $1804万
 $21,344/呎
-(26年-01月-04日)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -29890,7 +29894,7 @@
           <t>D | 844呎 (2房)
 $1657万
 $19,637/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
     </row>
@@ -29905,7 +29909,7 @@
           <t>A | 1118呎 (3房)
 $2438万
 $21,803/呎
-(25年-11月-18日)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -29913,7 +29917,7 @@
           <t>B | 1153呎 (3房)
 $2428万
 $21,062/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -29921,7 +29925,7 @@
           <t>C | 845呎 (2房)
 $1800万
 $21,302/呎
-(25年-12月-16日)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -29929,7 +29933,7 @@
           <t>D | 844呎 (2房)
 $1653万
 $19,581/呎
-(26年-03月-04日)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
     </row>
@@ -29944,7 +29948,7 @@
           <t>A | 1118呎 (3房)
 $2419万
 $21,638/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -29952,7 +29956,7 @@
           <t>B | 1153呎 (3房)
 $2397万
 $20,789/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -29960,7 +29964,7 @@
           <t>C | 934呎 (2房)
 $2852万
 $30,538/呎
-(20年-07月-21日)</t>
+(20年-07月-22日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -29968,7 +29972,7 @@
           <t>D | 844呎 (2房)
 $1648万
 $19,525/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
     </row>
@@ -29983,7 +29987,7 @@
           <t>A | 1228呎 (3房)
 $3513万
 $28,610/呎
-(20年-06月-11日)</t>
+(20年-06月-12日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -29991,7 +29995,7 @@
           <t>B | 1153呎 (3房)
 $2384万
 $20,676/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -29999,7 +30003,7 @@
           <t>C | 845呎 (2房)
 $2824万
 $33,422/呎
-(20年-05月-31日)</t>
+(20年-06月-01日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -30007,7 +30011,7 @@
           <t>D | 939呎 (2房)
 $2644万
 $28,160/呎
-(20年-05月-19日)</t>
+(20年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -30022,7 +30026,7 @@
           <t>A | 1118呎 (3房)
 $2395万
 $21,419/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -30030,7 +30034,7 @@
           <t>B | 1153呎 (3房)
 $2359万
 $20,460/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -30038,7 +30042,7 @@
           <t>C | 845呎 (2房)
 $1775万
 $21,001/呎
-(24年-04月-25日)</t>
+(24年-04月-26日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -30046,7 +30050,7 @@
           <t>D | 844呎 (2房)
 $1624万
 $19,247/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -30061,7 +30065,7 @@
           <t>A | 1118呎 (3房)
 $2368万
 $21,177/呎
-(25年-01月-05日)</t>
+(25年-01月-06日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -30069,7 +30073,7 @@
           <t>B | 1153呎 (3房)
 $2297万
 $19,919/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -30077,7 +30081,7 @@
           <t>C | 845呎 (2房)
 $1765万
 $20,891/呎
-(26年-01月-15日)</t>
+(26年-01月-16日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -30085,7 +30089,7 @@
           <t>D | 844呎 (2房)
 $1620万
 $19,192/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
     </row>
@@ -30100,7 +30104,7 @@
           <t>A | 1118呎 (3房)
 $2364万
 $21,144/呎
-(24年-10月-27日)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -30108,7 +30112,7 @@
           <t>B | 1153呎 (3房)
 $2297万
 $19,919/呎
-(26年-01月-18日)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -30116,7 +30120,7 @@
           <t>C | 845呎 (2房)
 $1763万
 $20,869/呎
-(26年-02月-24日)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -30124,7 +30128,7 @@
           <t>D | 844呎 (2房)
 $1619万
 $19,181/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -30139,7 +30143,7 @@
           <t>A | 1118呎 (3房)
 $2337万
 $20,902/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -30147,7 +30151,7 @@
           <t>B | 1153呎 (3房)
 $2290万
 $19,864/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -30155,7 +30159,7 @@
           <t>C | 845呎 (2房)
 $1756万
 $20,780/呎
-(26年-03月-04日)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -30163,7 +30167,7 @@
           <t>D | 844呎 (2房)
 $1619万
 $19,181/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -30178,7 +30182,7 @@
           <t>A | 1118呎 (3房)
 $2313万
 $20,691/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -30186,7 +30190,7 @@
           <t>B | 1153呎 (3房)
 $2284万
 $19,810/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -30194,7 +30198,7 @@
           <t>C | 829呎 (2房)
 $1726万
 $20,818/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -30202,7 +30206,7 @@
           <t>D | 844呎 (2房)
 $1618万
 $19,169/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -30283,22 +30287,22 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -30376,7 +30380,64 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>C | 890呎 (2房)
+招标单位
+-
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
+        <is>
+          <t>D | 898呎 (2房)
+招标单位
+-
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 2403呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 890呎 (2房)
 -
@@ -30384,40 +30445,22 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
-        <is>
-          <t>D | 898呎 (2房)
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 892呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 2403呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30425,7 +30468,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30433,30 +30476,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>C | 890呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$2065万
+$25,397/呎
+(26年-07月-27日)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 892呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
+$2014万
+$22,576/呎
+(26年-07月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30464,7 +30507,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30472,30 +30515,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$2065万
-$25,397/呎
-(26年-07月-05日)</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
+$2031万
+$24,981/呎
+(26年-07月-27日)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 892呎 (2房)
-$2014万
-$22,576/呎
-(26年-07月-19日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
+$1987万
+$22,274/呎
+(26年-07月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30503,7 +30546,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30511,30 +30554,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>C | 890呎 (2房)
-$2031万
-$22,820/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>D | 892呎 (2房)
-$1987万
-$22,274/呎
-(26年-07月-19日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$2011万
+$24,740/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 812呎 (2房)
+$1962万
+$24,167/呎
+(26年-07月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30542,7 +30585,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30550,30 +30593,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$2011万
-$24,740/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="inlineStr">
+$2003万
+$24,637/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$1962万
-$24,167/呎
-(26年-07月-16日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
+$1953万
+$24,058/呎
+(26年-07月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30581,7 +30624,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30589,30 +30632,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$2003万
-$24,637/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
+$1878万
+$23,098/呎
+(26年-05月-28日)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$1953万
-$24,058/呎
-(26年-07月-09日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
+$1838万
+$22,630/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30620,7 +30663,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30628,30 +30671,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$1878万
-$23,098/呎
-(26年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
+$1863万
+$22,912/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$1838万
-$22,630/呎
-(26年-06月-07日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
+$1829万
+$22,520/呎
+(26年-06月-15日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30659,7 +30702,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30667,30 +30710,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$1863万
-$22,912/呎
-(26年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
+$1927万
+$23,700/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$1829万
-$22,520/呎
-(26年-06月-14日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
+$1882万
+$23,177/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30698,7 +30741,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30706,30 +30749,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$1927万
-$23,700/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
+$1829万
+$22,496/呎
+(26年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$1882万
-$23,177/呎
-(26年-07月-01日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
+$1797万
+$22,135/呎
+(26年-06月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30737,7 +30780,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30745,30 +30788,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$1829万
-$22,496/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
+$1816万
+$22,332/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$1797万
-$22,135/呎
-(26年-06月-11日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
+$1793万
+$22,080/呎
+(26年-06月-23日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30776,7 +30819,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30784,30 +30827,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$1816万
-$22,332/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
+$1798万
+$22,113/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$1793万
-$22,080/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
+$1869万
+$23,014/呎
+(26年-07月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30815,7 +30858,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30823,30 +30866,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
-$1798万
-$22,113/呎
-(26年-06月-07日)</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
+$1860万
+$22,879/呎
+(26年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 812呎 (2房)
-$1869万
-$23,014/呎
-(26年-07月-09日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
+$1860万
+$22,904/呎
+(26年-07月-21日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
 -
@@ -30854,7 +30897,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 1398呎 (3房)
 -
@@ -30862,59 +30905,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$1860万
-$22,879/呎
-(26年-07月-14日)</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
-        <is>
-          <t>D | 812呎 (2房)
-$1860万
-$22,904/呎
-(26年-07月-20日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 890呎 (2房)
 $1865万
 $20,950/呎
-(26年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="E20" s="22" t="inlineStr">
+(26年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="inlineStr">
         <is>
           <t>D | 892呎 (2房)
+招标单位
 -
--
-(待售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -31093,7 +31097,7 @@
           <t>C | 1595呎 (4+房)
 $4779万
 $29,964/呎
-(25年-01月-27日)</t>
+(25年-01月-28日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr"/>
@@ -31111,7 +31115,7 @@
           <t>C | 808呎 (2房)
 $1924万
 $23,811/呎
-(24年-03月-17日)</t>
+(24年-03月-18日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -31119,7 +31123,7 @@
           <t>D | 808呎 (2房)
 $1934万
 $23,931/呎
-(24年-02月-01日)</t>
+(24年-02月-02日)</t>
         </is>
       </c>
     </row>
@@ -31135,7 +31139,7 @@
           <t>B | 2905呎 (4+房)
 $9870万
 $33,976/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -31153,7 +31157,7 @@
           <t>B | 1264呎 (3房)
 $3021万
 $23,902/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -31161,7 +31165,7 @@
           <t>C | 808呎 (2房)
 $1912万
 $23,663/呎
-(24年-03月-21日)</t>
+(24年-03月-22日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -31169,7 +31173,7 @@
           <t>D | 808呎 (2房)
 $1916万
 $23,712/呎
-(24年-01月-11日)</t>
+(24年-01月-12日)</t>
         </is>
       </c>
     </row>
@@ -31184,7 +31188,7 @@
           <t>A | 2258呎 (4+房)
 $7128万
 $31,568/呎
-(26年-01月-26日)</t>
+(26年-01月-27日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr"/>
@@ -31202,7 +31206,7 @@
           <t>A | 1266呎 (3房)
 $3067万
 $24,230/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -31210,7 +31214,7 @@
           <t>B | 1264呎 (3房)
 $3043万
 $24,074/呎
-(24年-04月-08日)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -31218,7 +31222,7 @@
           <t>C | 808呎 (2房)
 $1883万
 $23,308/呎
-(23年-12月-11日)</t>
+(23年-12月-12日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -31226,7 +31230,7 @@
           <t>D | 808呎 (2房)
 $1903万
 $23,547/呎
-(24年-01月-17日)</t>
+(24年-01月-18日)</t>
         </is>
       </c>
     </row>
@@ -31241,7 +31245,7 @@
           <t>A | 1266呎 (3房)
 $2983万
 $23,562/呎
-(24年-03月-19日)</t>
+(24年-03月-20日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -31249,7 +31253,7 @@
           <t>B | 1264呎 (3房)
 $2891万
 $22,873/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -31257,7 +31261,7 @@
           <t>C | 878呎 (2房)
 $1844万
 $21,000/呎
-(23年-11月-21日)</t>
+(23年-11月-22日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -31265,7 +31269,7 @@
           <t>D | 887呎 (2房)
 $1836万
 $20,700/呎
-(23年-10月-16日)</t>
+(23年-10月-17日)</t>
         </is>
       </c>
     </row>
@@ -31280,7 +31284,7 @@
           <t>A | 1266呎 (3房)
 $2805万
 $22,158/呎
-(26年-01月-25日)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -31288,7 +31292,7 @@
           <t>B | 1264呎 (3房)
 $2789万
 $22,065/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -31296,7 +31300,7 @@
           <t>C | 878呎 (2房)
 $1809万
 $20,600/呎
-(23年-11月-12日)</t>
+(23年-11月-13日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -31304,7 +31308,7 @@
           <t>D | 887呎 (2房)
 $1836万
 $20,700/呎
-(23年-11月-01日)</t>
+(23年-11月-02日)</t>
         </is>
       </c>
     </row>
@@ -31319,7 +31323,7 @@
           <t>A | 1266呎 (3房)
 $2832万
 $22,366/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -31327,7 +31331,7 @@
           <t>B | 1264呎 (3房)
 $2815万
 $22,272/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -31335,7 +31339,7 @@
           <t>C | 878呎 (2房)
 $1789万
 $20,380/呎
-(23年-10月-26日)</t>
+(23年-10月-27日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -31343,7 +31347,7 @@
           <t>D | 887呎 (2房)
 $1827万
 $20,600/呎
-(23年-10月-26日)</t>
+(23年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -31358,7 +31362,7 @@
           <t>A | 1266呎 (3房)
 $2804万
 $22,147/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -31366,7 +31370,7 @@
           <t>B | 1264呎 (3房)
 $2815万
 $22,272/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -31374,7 +31378,7 @@
           <t>C | 878呎 (2房)
 $1778万
 $20,251/呎
-(23年-10月-24日)</t>
+(23年-10月-25日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -31382,7 +31386,7 @@
           <t>D | 887呎 (2房)
 $1801万
 $20,308/呎
-(23年-11月-05日)</t>
+(23年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -31397,7 +31401,7 @@
           <t>A | 1266呎 (3房)
 $2755万
 $21,763/呎
-(26年-01月-25日)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -31405,7 +31409,7 @@
           <t>B | 1264呎 (3房)
 $2726万
 $21,562/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -31413,7 +31417,7 @@
           <t>C | 808呎 (2房)
 $1757万
 $21,741/呎
-(23年-10月-11日)</t>
+(23年-10月-12日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -31421,7 +31425,7 @@
           <t>D | 808呎 (2房)
 $1775万
 $21,964/呎
-(23年-10月-11日)</t>
+(23年-10月-12日)</t>
         </is>
       </c>
     </row>
@@ -31436,7 +31440,7 @@
           <t>A | 1266呎 (3房)
 $2720万
 $21,489/呎
-(26年-01月-05日)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -31444,7 +31448,7 @@
           <t>B | 1380呎 (3房)
 $2892万
 $20,960/呎
-(24年-03月-26日)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -31452,7 +31456,7 @@
           <t>C | 878呎 (2房)
 $1782万
 $20,296/呎
-(23年-11月-09日)</t>
+(23年-11月-10日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -31460,7 +31464,7 @@
           <t>D | 808呎 (2房)
 $1756万
 $21,738/呎
-(23年-10月-19日)</t>
+(23年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -31475,7 +31479,7 @@
           <t>A | 1266呎 (3房)
 $2885万
 $22,791/呎
-(24年-04月-01日)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -31483,7 +31487,7 @@
           <t>B | 1380呎 (3房)
 $2867万
 $20,774/呎
-(24年-04月-01日)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -31491,7 +31495,7 @@
           <t>C | 878呎 (2房)
 $1760万
 $20,050/呎
-(23年-10月-25日)</t>
+(23年-10月-26日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -31499,7 +31503,7 @@
           <t>D | 887呎 (2房)
 $1747万
 $19,700/呎
-(23年-10月-26日)</t>
+(23年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -31514,7 +31518,7 @@
           <t>A | 1266呎 (3房)
 $2679万
 $21,160/呎
-(25年-04月-10日)</t>
+(25年-04月-11日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -31522,7 +31526,7 @@
           <t>B | 1264呎 (3房)
 $2663万
 $21,071/呎
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -31530,7 +31534,7 @@
           <t>C | 878呎 (2房)
 $1668万
 $19,000/呎
-(23年-10月-16日)</t>
+(23年-10月-17日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -31538,7 +31542,7 @@
           <t>D | 808呎 (2房)
 $1774万
 $21,955/呎
-(23年-12月-07日)</t>
+(23年-12月-08日)</t>
         </is>
       </c>
     </row>
@@ -31553,7 +31557,7 @@
           <t>A | 1388呎 (3房)
 $2720万
 $19,600/呎
-(23年-10月-18日)</t>
+(23年-10月-19日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -31561,7 +31565,7 @@
           <t>B | 1380呎 (3房)
 $2705万
 $19,600/呎
-(23年-10月-29日)</t>
+(23年-10月-30日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -31569,7 +31573,7 @@
           <t>C | 808呎 (2房)
 $1743万
 $21,570/呎
-(23年-12月-10日)</t>
+(23年-12月-11日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -31577,7 +31581,7 @@
           <t>D | 808呎 (2房)
 $1761万
 $21,791/呎
-(23年-12月-06日)</t>
+(23年-12月-07日)</t>
         </is>
       </c>
     </row>
@@ -31592,7 +31596,7 @@
           <t>A | 1388呎 (3房)
 $2769万
 $19,950/呎
-(23年-11月-26日)</t>
+(23年-11月-27日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -31600,7 +31604,7 @@
           <t>B | 1264呎 (3房)
 $2839万
 $22,462/呎
-(23年-12月-03日)</t>
+(23年-12月-04日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -31608,7 +31612,7 @@
           <t>C | 878呎 (2房)
 $1708万
 $19,450/呎
-(23年-12月-04日)</t>
+(23年-12月-05日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -31616,7 +31620,7 @@
           <t>D | 887呎 (2房)
 $1730万
 $19,500/呎
-(23年-10月-30日)</t>
+(23年-10月-31日)</t>
         </is>
       </c>
     </row>
@@ -31631,7 +31635,7 @@
           <t>A | 1388呎 (3房)
 $2693万
 $19,400/呎
-(23年-11月-14日)</t>
+(23年-11月-15日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -31639,7 +31643,7 @@
           <t>B | 1264呎 (3房)
 $2677万
 $21,180/呎
-(23年-11月-14日)</t>
+(23年-11月-15日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -31647,7 +31651,7 @@
           <t>C | 808呎 (2房)
 $1710万
 $21,168/呎
-(23年-12月-18日)</t>
+(23年-12月-19日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -31655,7 +31659,7 @@
           <t>D | 808呎 (2房)
 $1762万
 $21,803/呎
-(23年-12月-03日)</t>
+(23年-12月-04日)</t>
         </is>
       </c>
     </row>
@@ -31670,7 +31674,7 @@
           <t>A | 1266呎 (3房)
 $2741万
 $21,653/呎
-(23年-12月-18日)</t>
+(23年-12月-19日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -31678,7 +31682,7 @@
           <t>B | 1264呎 (3房)
 $2732万
 $21,617/呎
-(24年-02月-07日)</t>
+(24年-02月-08日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -31686,7 +31690,7 @@
           <t>C | 808呎 (2房)
 $1677万
 $20,755/呎
-(24年-03月-27日)</t>
+(24年-03月-28日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -31694,7 +31698,7 @@
           <t>D | 887呎 (2房)
 $1685万
 $19,000/呎
-(23年-10月-23日)</t>
+(23年-10月-24日)</t>
         </is>
       </c>
     </row>
@@ -31709,7 +31713,7 @@
           <t>A | 1250呎 (3房)
 $2483万
 $19,866/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -31717,7 +31721,7 @@
           <t>B | 1264呎 (3房)
 $2484万
 $19,652/呎
-(25年-05月-19日)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -31725,7 +31729,7 @@
           <t>C | 753呎 (2房)
 $1566万
 $20,797/呎
-(24年-04月-09日)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -31733,7 +31737,7 @@
           <t>D | 753呎 (2房)
 $1583万
 $21,019/呎
-(24年-04月-14日)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -31866,7 +31870,7 @@
           <t>B | 3236呎 (4+房)
 $11446万
 $35,371/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -31890,7 +31894,7 @@
           <t>B | 1352呎 (3房)
 $3628万
 $26,833/呎
-(26年-01月-18日)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -31898,7 +31902,7 @@
           <t>C | 785呎 (2房)
 $1849万
 $23,558/呎
-(24年-06月-16日)</t>
+(24年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -31913,7 +31917,7 @@
           <t>A | 2271呎 (4+房)
 $7508万
 $33,060/呎
-(25年-11月-23日)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr"/>
@@ -31930,7 +31934,7 @@
           <t>A | 1321呎 (3房)
 $3526万
 $26,694/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -31938,7 +31942,7 @@
           <t>B | 1340呎 (3房)
 $3558万
 $26,551/呎
-(26年-01月-18日)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -31946,7 +31950,7 @@
           <t>C | 785呎 (2房)
 $1833万
 $23,350/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -31961,7 +31965,7 @@
           <t>A | 1321呎 (3房)
 $3484万
 $26,376/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -31969,7 +31973,7 @@
           <t>B | 1340呎 (3房)
 $3139万
 $23,428/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -31977,7 +31981,7 @@
           <t>C | 785呎 (2房)
 $1798万
 $22,911/呎
-(24年-05月-06日)</t>
+(24年-05月-07日)</t>
         </is>
       </c>
     </row>
@@ -32008,7 +32012,7 @@
           <t>C | 785呎 (2房)
 $1778万
 $22,644/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -32023,7 +32027,7 @@
           <t>A | 1321呎 (3房)
 $3115万
 $23,584/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -32031,7 +32035,7 @@
           <t>B | 1340呎 (3房)
 $3136万
 $23,400/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -32039,7 +32043,7 @@
           <t>C | 785呎 (2房)
 $1754万
 $22,340/呎
-(24年-04月-11日)</t>
+(24年-04月-12日)</t>
         </is>
       </c>
     </row>
@@ -32054,7 +32058,7 @@
           <t>A | 1321呎 (3房)
 $3110万
 $23,544/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -32070,7 +32074,7 @@
           <t>C | 785呎 (2房)
 $1618万
 $20,611/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
     </row>
@@ -32085,7 +32089,7 @@
           <t>A | 1321呎 (3房)
 $3082万
 $23,332/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -32101,7 +32105,7 @@
           <t>C | 785呎 (2房)
 $1598万
 $20,357/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
     </row>
@@ -32116,7 +32120,7 @@
           <t>A | 1321呎 (3房)
 $3050万
 $23,089/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -32132,7 +32136,7 @@
           <t>C | 785呎 (2房)
 $1569万
 $19,985/呎
-(25年-05月-21日)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -32147,7 +32151,7 @@
           <t>A | 1321呎 (3房)
 $3030万
 $22,940/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -32155,7 +32159,7 @@
           <t>B | 1340呎 (3房)
 $3030万
 $22,612/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -32163,7 +32167,7 @@
           <t>C | 785呎 (2房)
 $1567万
 $19,963/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
     </row>
@@ -32178,7 +32182,7 @@
           <t>A | 1401呎 (3房)
 $3512万
 $25,070/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -32186,7 +32190,7 @@
           <t>B | 1415呎 (3房)
 $3141万
 $22,200/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -32194,7 +32198,7 @@
           <t>C | 785呎 (2房)
 $1543万
 $19,661/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
     </row>
@@ -32209,7 +32213,7 @@
           <t>A | 1321呎 (3房)
 $2988万
 $22,621/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -32217,7 +32221,7 @@
           <t>B | 1340呎 (3房)
 $2990万
 $22,313/呎
-(26年-06月-22日)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -32225,7 +32229,7 @@
           <t>C | 785呎 (2房)
 $1539万
 $19,607/呎
-(26年-03月-03日)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
     </row>
@@ -32240,7 +32244,7 @@
           <t>A | 1321呎 (3房)
 $3068万
 $23,226/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -32256,7 +32260,7 @@
           <t>C | 785呎 (2房)
 $1526万
 $19,445/呎
-(26年-01月-07日)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
     </row>
@@ -32271,7 +32275,7 @@
           <t>A | 1321呎 (3房)
 $2921万
 $22,113/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -32287,7 +32291,7 @@
           <t>C | 785呎 (2房)
 $1522万
 $19,391/呎
-(26年-01月-21日)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
     </row>
@@ -32302,7 +32306,7 @@
           <t>A | 1321呎 (3房)
 $2928万
 $22,166/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -32318,7 +32322,7 @@
           <t>C | 785呎 (2房)
 $1509万
 $19,229/呎
-(26年-01月-18日)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
     </row>
@@ -32349,7 +32353,7 @@
           <t>C | 785呎 (2房)
 $1503万
 $19,142/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
     </row>

--- a/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
+++ b/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
@@ -16107,7 +16107,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -19589,7 +19589,7 @@
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -29326,10 +29326,35 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1984万
+$23,479/呎
+(25年-03月-11日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 845呎 (2房)
+$1873万
+$22,169/呎
+(25年-07月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 3255呎 (4+房)
 $11039万
@@ -29337,34 +29362,9 @@
 (25年-02月-26日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
       <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1984万
-$23,479/呎
-(25年-03月-11日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 845呎 (2房)
-$1873万
-$22,169/呎
-(25年-07月-11日)</t>
-        </is>
-      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30282,12 +30282,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -30368,11 +30368,29 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 2403呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1399呎 (3房)
 -
@@ -30380,15 +30398,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>C | 890呎 (2房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E6" s="25" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>D | 898呎 (2房)
 招标单位
@@ -30397,24 +30415,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 2403呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -30913,12 +30913,12 @@
 (26年-07月-17日)</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>D | 892呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -31885,11 +31885,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2271呎 (4+房)
+$7508万
+$33,060/呎
+(25年-11月-24日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1352呎 (3房)
 $3628万
@@ -31897,7 +31914,7 @@
 (26年-01月-19日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 785呎 (2房)
 $1849万
@@ -31905,23 +31922,6 @@
 (24年-06月-17日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2271呎 (4+房)
-$7508万
-$33,060/呎
-(25年-11月-24日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
+++ b/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
@@ -27626,10 +27626,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1442呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28&amp;29</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 6681呎 (4+房)
 -
@@ -27637,32 +27661,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>B | 1442呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -28476,10 +28476,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1351呎 (3房)
+$3630万
+$26,866/呎
+(24年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2612万
+$22,139/呎
+(25年-09月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2338呎 (4+房)
 $7600万
@@ -28487,32 +28511,8 @@
 (24年-04月-09日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1351呎 (3房)
-$3630万
-$26,866/呎
-(24年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2612万
-$22,139/呎
-(25年-09月-12日)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -29326,12 +29326,30 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 3255呎 (4+房)
+$11039万
+$33,915/呎
+(25年-02月-26日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 845呎 (2房)
 $1984万
@@ -29339,7 +29357,7 @@
 (25年-03月-11日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 845呎 (2房)
 $1873万
@@ -29347,24 +29365,6 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 3255呎 (4+房)
-$11039万
-$33,915/呎
-(25年-02月-26日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -31148,11 +31148,29 @@
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 2258呎 (4+房)
+$7128万
+$31,568/呎
+(26年-01月-27日)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr"/>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 1264呎 (3房)
 $3021万
@@ -31160,7 +31178,7 @@
 (25年-10月-08日)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 808呎 (2房)
 $1912万
@@ -31168,7 +31186,7 @@
 (24年-03月-22日)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (2房)
 $1916万
@@ -31176,24 +31194,6 @@
 (24年-01月-12日)</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>A | 2258呎 (4+房)
-$7128万
-$31,568/呎
-(26年-01月-27日)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">

--- a/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
+++ b/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -141,11 +141,6 @@
       <color rgb="00000000"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -223,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -295,9 +290,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2199,23 +2191,19 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>32648300</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>26098</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2224,12 +2212,12 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -2239,7 +2227,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4385,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>1251</v>
+        <v>1186</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4413,7 +4401,7 @@
         <v>26896500</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>21500</v>
+        <v>22678</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -15967,7 +15955,7 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -15977,12 +15965,12 @@
       </c>
       <c r="H232" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I232" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J232" s="3" t="inlineStr">
@@ -15992,12 +15980,12 @@
       </c>
       <c r="K232" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L232" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M232" s="3" t="inlineStr">
@@ -16007,7 +15995,7 @@
       </c>
       <c r="N232" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -16037,23 +16025,19 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H233" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I233" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H233" s="5" t="n">
+        <v>20833600</v>
+      </c>
+      <c r="I233" s="5" t="n">
+        <v>23200</v>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
@@ -16062,12 +16046,12 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M233" s="3" t="inlineStr">
@@ -16077,7 +16061,7 @@
       </c>
       <c r="N233" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -16107,23 +16091,19 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H234" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I234" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H234" s="5" t="n">
+        <v>21271000</v>
+      </c>
+      <c r="I234" s="5" t="n">
+        <v>23900</v>
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
@@ -16132,12 +16112,12 @@
       </c>
       <c r="K234" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M234" s="3" t="inlineStr">
@@ -16147,7 +16127,7 @@
       </c>
       <c r="N234" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -16177,23 +16157,19 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H235" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I235" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H235" s="5" t="n">
+        <v>33980000</v>
+      </c>
+      <c r="I235" s="5" t="n">
+        <v>24289</v>
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
@@ -19589,23 +19565,19 @@
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H285" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I285" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H285" s="5" t="n">
+        <v>18553600</v>
+      </c>
+      <c r="I285" s="5" t="n">
+        <v>20800</v>
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
@@ -19614,12 +19586,12 @@
       </c>
       <c r="K285" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L285" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M285" s="3" t="inlineStr">
@@ -19629,7 +19601,7 @@
       </c>
       <c r="N285" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -19865,7 +19837,7 @@
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -19875,12 +19847,12 @@
       </c>
       <c r="H289" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I289" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J289" s="3" t="inlineStr">
@@ -19890,12 +19862,12 @@
       </c>
       <c r="K289" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L289" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M289" s="3" t="inlineStr">
@@ -19905,7 +19877,7 @@
       </c>
       <c r="N289" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -25235,7 +25207,7 @@
       </c>
       <c r="F370" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G370" s="3" t="inlineStr">
@@ -25245,12 +25217,12 @@
       </c>
       <c r="H370" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I370" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J370" s="3" t="inlineStr">
@@ -25260,12 +25232,12 @@
       </c>
       <c r="K370" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L370" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M370" s="3" t="inlineStr">
@@ -25275,7 +25247,7 @@
       </c>
       <c r="N370" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -26369,7 +26341,7 @@
         </is>
       </c>
       <c r="E387" s="4" t="n">
-        <v>1415</v>
+        <v>1340</v>
       </c>
       <c r="F387" s="3" t="inlineStr">
         <is>
@@ -26378,14 +26350,14 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
         <v>31413000</v>
       </c>
       <c r="I387" s="5" t="n">
-        <v>22200</v>
+        <v>23443</v>
       </c>
       <c r="J387" s="3" t="inlineStr">
         <is>
@@ -26435,7 +26407,7 @@
         </is>
       </c>
       <c r="E388" s="4" t="n">
-        <v>1401</v>
+        <v>1321</v>
       </c>
       <c r="F388" s="3" t="inlineStr">
         <is>
@@ -26451,7 +26423,7 @@
         <v>35122500</v>
       </c>
       <c r="I388" s="5" t="n">
-        <v>25070</v>
+        <v>26588</v>
       </c>
       <c r="J388" s="3" t="inlineStr">
         <is>
@@ -26901,7 +26873,7 @@
         </is>
       </c>
       <c r="E395" s="4" t="n">
-        <v>785</v>
+        <v>848</v>
       </c>
       <c r="F395" s="3" t="inlineStr">
         <is>
@@ -26917,7 +26889,7 @@
         <v>15221600</v>
       </c>
       <c r="I395" s="5" t="n">
-        <v>19391</v>
+        <v>17950</v>
       </c>
       <c r="J395" s="3" t="inlineStr">
         <is>
@@ -27560,7 +27532,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27570,7 +27542,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27865,7 +27837,131 @@
 (25年-04月-23日)</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+$3265万
+$26,098/呎
+(26年-08月-04日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3417万
+$24,999/呎
+(24年-12月-10日)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3340万
+$24,415/呎
+(25年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2753万
+$23,210/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3396万
+$24,841/呎
+(24年-11月-21日)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3321万
+$24,275/呎
+(25年-07月-22日)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2852万
+$24,050/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3403万
+$24,894/呎
+(24年-12月-24日)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3313万
+$24,218/呎
+(25年-06月-13日)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2830万
+$23,860/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$4198万
+$30,710/呎
+(26年-02月-10日)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3270万
+$23,905/呎
+(25年-08月-07日)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 招标单位
@@ -27874,122 +27970,122 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3417万
-$24,999/呎
-(24年-12月-10日)</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
+$3374万
+$24,682/呎
+(25年-01月-03日)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3340万
-$24,415/呎
-(25年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
+$3227万
+$23,588/呎
+(24年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 1186呎 (3房)
-$2753万
-$23,210/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
+$2792万
+$23,543/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3396万
-$24,841/呎
-(24年-11月-21日)</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3321万
-$24,275/呎
-(25年-07月-22日)</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2852万
-$24,050/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3403万
-$24,894/呎
-(24年-12月-24日)</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3313万
-$24,218/呎
+$3665万
+$26,811/呎
 (25年-06月-13日)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2830万
-$23,860/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$4198万
-$30,710/呎
-(26年-02月-10日)</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
 $3270万
 $23,905/呎
-(25年-08月-07日)</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2815万
+$23,733/呎
+(26年-07月-28日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3338万
+$24,418/呎
+(25年-11月-20日)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3205万
+$23,429/呎
+(25年-08月-15日)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3330万
+$24,360/呎
+(25年-11月-19日)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3212万
+$23,482/呎
+(26年-03月-30日)</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 招标单位
@@ -27998,91 +28094,60 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3374万
-$24,682/呎
-(25年-01月-03日)</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
+$3352万
+$24,524/呎
+(25年-12月-17日)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3227万
-$23,588/呎
-(24年-08月-23日)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2792万
-$23,543/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
+$3209万
+$23,461/呎
+(26年-04月-13日)</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3665万
-$26,811/呎
-(25年-06月-13日)</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
+$3324万
+$24,312/呎
+(24年-04月-12日)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3270万
-$23,905/呎
-(26年-04月-20日)</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2815万
-$23,733/呎
-(26年-07月-28日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3338万
-$24,418/呎
-(25年-11月-20日)</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3205万
-$23,429/呎
-(25年-08月-15日)</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
+$3193万
+$23,342/呎
+(24年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -28091,99 +28156,6 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3330万
-$24,360/呎
-(25年-11月-19日)</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3212万
-$23,482/呎
-(26年-03月-30日)</t>
-        </is>
-      </c>
-      <c r="D22" s="23" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3352万
-$24,524/呎
-(25年-12月-17日)</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3209万
-$23,461/呎
-(26年-04月-13日)</t>
-        </is>
-      </c>
-      <c r="D23" s="23" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3324万
-$24,312/呎
-(24年-04月-12日)</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3193万
-$23,342/呎
-(24年-04月-08日)</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
         <is>
@@ -28208,9 +28180,9 @@
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t>C | 1251呎 (3房)
+          <t>C | 1186呎 (3房)
 $2690万
-$21,500/呎
+$22,678/呎
 (26年-07月-20日)</t>
         </is>
       </c>
@@ -30287,12 +30259,12 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -30302,7 +30274,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -30340,12 +30312,12 @@
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>B | 3100呎 (4+房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -30390,28 +30362,28 @@
         </is>
       </c>
       <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1399呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
+$3398万
+$24,289/呎
+(26年-08月-08日)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 890呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E7" s="25" t="inlineStr">
+$2127万
+$23,900/呎
+(26年-08月-03日)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 898呎 (2房)
-招标单位
--
-(已定价未售)</t>
+$2083万
+$23,200/呎
+(26年-08月-04日)</t>
         </is>
       </c>
     </row>
@@ -30913,51 +30885,51 @@
 (26年-07月-17日)</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 892呎 (2房)
+$1855万
+$20,800/呎
+(26年-08月-03日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 1399呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 1382呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 890呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 892呎 (2房)
 招标单位
 -
 (在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t>A | 1399呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
-        <is>
-          <t>B | 1382呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
-        <is>
-          <t>C | 890呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="22" t="inlineStr">
-        <is>
-          <t>D | 892呎 (2房)
--
--
-(待售)</t>
         </is>
       </c>
     </row>
@@ -31148,10 +31120,42 @@
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr"/>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 1264呎 (3房)
+$3021万
+$23,902/呎
+(25年-10月-08日)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1912万
+$23,663/呎
+(24年-03月-22日)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1916万
+$23,712/呎
+(24年-01月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
           <t>19&amp;20</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 2258呎 (4+房)
 $7128万
@@ -31159,41 +31163,9 @@
 (26年-01月-27日)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr"/>
-      <c r="D8" s="20" t="inlineStr"/>
-      <c r="E8" s="20" t="inlineStr"/>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>B | 1264呎 (3房)
-$3021万
-$23,902/呎
-(25年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1912万
-$23,663/呎
-(24年-03月-22日)</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1916万
-$23,712/呎
-(24年-01月-12日)</t>
-        </is>
-      </c>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -31812,7 +31784,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -31832,7 +31804,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -31991,12 +31963,12 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 1401呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -32179,18 +32151,18 @@
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>A | 1401呎 (3房)
+          <t>A | 1321呎 (3房)
 $3512万
-$25,070/呎
+$26,588/呎
 (26年-07月-17日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>B | 1415呎 (3房)
+          <t>B | 1340呎 (3房)
 $3141万
-$22,200/呎
-(26年-07月-17日)</t>
+$23,443/呎
+(26年-08月-10日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -32288,9 +32260,9 @@
       </c>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t>C | 785呎 (2房)
+          <t>C | 848呎 (2房)
 $1522万
-$19,391/呎
+$17,950/呎
 (26年-01月-22日)</t>
         </is>
       </c>

--- a/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
+++ b/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
@@ -3985,23 +3985,19 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>27396900</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>21900</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -4010,12 +4006,12 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -4025,7 +4021,7 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -16293,7 +16289,7 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -16303,12 +16299,12 @@
       </c>
       <c r="H237" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I237" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J237" s="3" t="inlineStr">
@@ -16318,12 +16314,12 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L237" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M237" s="3" t="inlineStr">
@@ -16333,7 +16329,7 @@
       </c>
       <c r="N237" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16565,7 @@
         </is>
       </c>
       <c r="E241" s="4" t="n">
-        <v>892</v>
+        <v>812</v>
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
@@ -16578,14 +16574,14 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
         <v>20138000</v>
       </c>
       <c r="I241" s="5" t="n">
-        <v>22576</v>
+        <v>24800</v>
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
@@ -16841,7 +16837,7 @@
         </is>
       </c>
       <c r="E245" s="4" t="n">
-        <v>892</v>
+        <v>812</v>
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
@@ -16850,14 +16846,14 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
         <v>19868000</v>
       </c>
       <c r="I245" s="5" t="n">
-        <v>22274</v>
+        <v>24468</v>
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
@@ -19627,7 +19623,7 @@
         </is>
       </c>
       <c r="E286" s="4" t="n">
-        <v>890</v>
+        <v>813</v>
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
@@ -19636,14 +19632,14 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
         <v>18645500</v>
       </c>
       <c r="I286" s="5" t="n">
-        <v>20950</v>
+        <v>22934</v>
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
@@ -19837,23 +19833,19 @@
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H289" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I289" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H289" s="5" t="n">
+        <v>18464400</v>
+      </c>
+      <c r="I289" s="5" t="n">
+        <v>20700</v>
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
@@ -19862,12 +19854,12 @@
       </c>
       <c r="K289" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L289" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M289" s="3" t="inlineStr">
@@ -19877,7 +19869,7 @@
       </c>
       <c r="N289" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -25207,23 +25199,19 @@
       </c>
       <c r="F370" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H370" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I370" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H370" s="5" t="n">
+        <v>33343800</v>
+      </c>
+      <c r="I370" s="5" t="n">
+        <v>23800</v>
       </c>
       <c r="J370" s="3" t="inlineStr">
         <is>
@@ -25232,12 +25220,12 @@
       </c>
       <c r="K370" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L370" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M370" s="3" t="inlineStr">
@@ -25247,7 +25235,7 @@
       </c>
       <c r="N370" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -26416,7 +26404,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -27532,7 +27520,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27542,7 +27530,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>57</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27598,11 +27586,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27&amp;28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 6681呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1442呎 (1房)
 -
@@ -27610,7 +27615,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -27619,23 +27624,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27&amp;28&amp;29</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 6681呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -28116,12 +28104,12 @@
 (26年-04月-13日)</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
-招标单位
--
-(在售)</t>
+$2740万
+$21,900/呎
+(26年-08月-10日)</t>
         </is>
       </c>
     </row>
@@ -28448,11 +28436,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2338呎 (4+房)
+$7600万
+$32,506/呎
+(24年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1351呎 (3房)
 $3630万
@@ -28460,7 +28465,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1180呎 (3房)
 $2612万
@@ -28468,23 +28473,6 @@
 (25年-09月-12日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2338呎 (4+房)
-$7600万
-$32,506/呎
-(24年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30264,7 +30252,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -30274,7 +30262,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -30417,12 +30405,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>D | 892呎 (2房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -30458,10 +30446,10 @@
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
-          <t>D | 892呎 (2房)
+          <t>D | 812呎 (2房)
 $2014万
-$22,576/呎
-(26年-07月-20日)</t>
+$24,800/呎
+(26年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -30497,10 +30485,10 @@
       </c>
       <c r="E10" s="21" t="inlineStr">
         <is>
-          <t>D | 892呎 (2房)
+          <t>D | 812呎 (2房)
 $1987万
-$22,274/呎
-(26年-07月-20日)</t>
+$24,468/呎
+(26年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -30879,10 +30867,10 @@
       </c>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t>C | 890呎 (2房)
+          <t>C | 813呎 (2房)
 $1865万
-$20,950/呎
-(26年-07月-17日)</t>
+$22,934/呎
+(26年-08月-10日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -30924,12 +30912,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 892呎 (2房)
-招标单位
--
-(在售)</t>
+$1846万
+$20,700/呎
+(26年-08月-10日)</t>
         </is>
       </c>
     </row>
@@ -31077,12 +31065,30 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>20&amp;21</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 2905呎 (4+房)
+$9870万
+$33,976/呎
+(26年-04月-13日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 808呎 (2房)
 $1924万
@@ -31090,7 +31096,7 @@
 (24年-03月-18日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (2房)
 $1934万
@@ -31098,24 +31104,6 @@
 (24年-02月-02日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>20&amp;21</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 2905呎 (4+房)
-$9870万
-$33,976/呎
-(26年-04月-13日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -31784,7 +31772,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -31794,7 +31782,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -31963,12 +31951,12 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 1401呎 (3房)
-招标单位
--
-(在售)</t>
+$3334万
+$23,800/呎
+(26年-08月-11日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -32154,7 +32142,7 @@
           <t>A | 1321呎 (3房)
 $3512万
 $26,588/呎
-(26年-07月-17日)</t>
+(26年-08月-10日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">

--- a/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
+++ b/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
@@ -27586,10 +27586,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1442呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28&amp;29</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 6681呎 (4+房)
 -
@@ -27597,32 +27621,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>B | 1442呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -29286,10 +29286,35 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1984万
+$23,479/呎
+(25年-03月-11日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 845呎 (2房)
+$1873万
+$22,169/呎
+(25年-07月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 3255呎 (4+房)
 $11039万
@@ -29297,34 +29322,9 @@
 (25年-02月-26日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
       <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1984万
-$23,479/呎
-(25年-03月-11日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 845呎 (2房)
-$1873万
-$22,169/呎
-(25年-07月-11日)</t>
-        </is>
-      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30328,10 +30328,42 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1399呎 (3房)
+$3398万
+$24,289/呎
+(26年-08月-08日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 890呎 (2房)
+$2127万
+$23,900/呎
+(26年-08月-03日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 898呎 (2房)
+$2083万
+$23,200/呎
+(26年-08月-04日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19&amp;20</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 2403呎 (4+房)
 -
@@ -30339,41 +30371,9 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1399呎 (3房)
-$3398万
-$24,289/呎
-(26年-08月-08日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 890呎 (2房)
-$2127万
-$23,900/呎
-(26年-08月-03日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 898呎 (2房)
-$2083万
-$23,200/呎
-(26年-08月-04日)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -31845,10 +31845,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1352呎 (3房)
+$3628万
+$26,833/呎
+(26年-01月-19日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1849万
+$23,558/呎
+(24年-06月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19&amp;20</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2271呎 (4+房)
 $7508万
@@ -31856,32 +31880,8 @@
 (25年-11月-24日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1352呎 (3房)
-$3628万
-$26,833/呎
-(26年-01月-19日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1849万
-$23,558/呎
-(24年-06月-17日)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
+++ b/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
@@ -27586,11 +27586,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27&amp;28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 6681呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1442呎 (1房)
 -
@@ -27598,7 +27615,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -27606,23 +27623,6 @@
 (待售)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27&amp;28&amp;29</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 6681呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -28436,10 +28436,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1351呎 (3房)
+$3630万
+$26,866/呎
+(24年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2612万
+$22,139/呎
+(25年-09月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2338呎 (4+房)
 $7600万
@@ -28447,32 +28471,8 @@
 (24年-04月-09日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1351呎 (3房)
-$3630万
-$26,866/呎
-(24年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2612万
-$22,139/呎
-(25年-09月-12日)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -29286,12 +29286,30 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 3255呎 (4+房)
+$11039万
+$33,915/呎
+(25年-02月-26日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 845呎 (2房)
 $1984万
@@ -29299,7 +29317,7 @@
 (25年-03月-11日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 845呎 (2房)
 $1873万
@@ -29307,24 +29325,6 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 3255呎 (4+房)
-$11039万
-$33,915/呎
-(25年-02月-26日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
+++ b/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
@@ -9075,7 +9075,7 @@
         </is>
       </c>
       <c r="E128" s="4" t="n">
-        <v>1347</v>
+        <v>1425</v>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>40857600</v>
       </c>
       <c r="I128" s="5" t="n">
-        <v>30332</v>
+        <v>28672</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
@@ -14298,14 +14298,14 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-05-08</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
-        <v>28242000</v>
+        <v>18213000</v>
       </c>
       <c r="I207" s="5" t="n">
-        <v>33422</v>
+        <v>21554</v>
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
@@ -15951,23 +15951,19 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H232" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I232" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H232" s="5" t="n">
+        <v>106640000</v>
+      </c>
+      <c r="I232" s="5" t="n">
+        <v>34400</v>
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
@@ -15976,12 +15972,12 @@
       </c>
       <c r="K232" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L232" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M232" s="3" t="inlineStr">
@@ -15991,7 +15987,7 @@
       </c>
       <c r="N232" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -16289,23 +16285,19 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H237" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I237" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H237" s="5" t="n">
+        <v>20382200</v>
+      </c>
+      <c r="I237" s="5" t="n">
+        <v>22850</v>
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
@@ -16314,12 +16306,12 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L237" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M237" s="3" t="inlineStr">
@@ -16329,7 +16321,7 @@
       </c>
       <c r="N237" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -28436,11 +28428,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2338呎 (4+房)
+$7600万
+$32,506/呎
+(24年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1351呎 (3房)
 $3630万
@@ -28448,7 +28457,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1180呎 (3房)
 $2612万
@@ -28457,23 +28466,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2338呎 (4+房)
-$7600万
-$32,506/呎
-(24年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -29017,9 +29009,9 @@
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>B | 1347呎 (3房)
+          <t>B | 1425呎 (3房)
 $4086万
-$30,332/呎
+$28,672/呎
 (20年-05月-18日)</t>
         </is>
       </c>
@@ -29286,10 +29278,35 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1984万
+$23,479/呎
+(25年-03月-11日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 845呎 (2房)
+$1873万
+$22,169/呎
+(25年-07月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 3255呎 (4+房)
 $11039万
@@ -29297,34 +29314,9 @@
 (25年-02月-26日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
       <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1984万
-$23,479/呎
-(25年-03月-11日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 845呎 (2房)
-$1873万
-$22,169/呎
-(25年-07月-11日)</t>
-        </is>
-      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -29961,9 +29953,9 @@
       <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 845呎 (2房)
-$2824万
-$33,422/呎
-(20年-06月-01日)</t>
+$1821万
+$21,554/呎
+(20年-05月-08日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -30242,7 +30234,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -30252,7 +30244,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -30300,12 +30292,12 @@
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>B | 3100呎 (4+房)
-招标单位
--
-(在售)</t>
+$10664万
+$34,400/呎
+(26年-08月-13日)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -30405,12 +30397,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 892呎 (2房)
-招标单位
--
-(在售)</t>
+$2038万
+$22,850/呎
+(26年-08月-14日)</t>
         </is>
       </c>
     </row>

--- a/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
+++ b/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1251</v>
+        <v>1186</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1796,14 +1796,14 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
         <v>33248700</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>26578</v>
+        <v>28034</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -16361,12 +16361,12 @@
       </c>
       <c r="H238" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I238" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J238" s="3" t="inlineStr">
@@ -16376,12 +16376,12 @@
       </c>
       <c r="K238" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L238" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M238" s="3" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="N238" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -17237,7 +17237,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -17247,12 +17247,12 @@
       </c>
       <c r="H251" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I251" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J251" s="3" t="inlineStr">
@@ -17262,12 +17262,12 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L251" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M251" s="3" t="inlineStr">
@@ -17277,7 +17277,7 @@
       </c>
       <c r="N251" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -17307,23 +17307,19 @@
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H252" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I252" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H252" s="5" t="n">
+        <v>32037100</v>
+      </c>
+      <c r="I252" s="5" t="n">
+        <v>22900</v>
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
@@ -25798,11 +25794,11 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
-        <v>30822200</v>
+        <v>30822000</v>
       </c>
       <c r="I379" s="5" t="n">
         <v>23332</v>
@@ -27578,10 +27574,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1442呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28&amp;29</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 6681呎 (4+房)
 -
@@ -27589,25 +27609,87 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>B | 1442呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 2669呎 (4+房)
+$7877万
+$29,514/呎
+(25年-03月-13日)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$3125万
+$26,347/呎
+(26年-01月-19日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3612万
+$26,426/呎
+(24年-07月-26日)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3618万
+$26,444/呎
+(24年-07月-26日)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$3002万
+$25,315/呎
+(26年-06月-04日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3500万
+$25,604/呎
+(24年-10月-10日)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3473万
+$25,386/呎
+(24年-12月-24日)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -27616,84 +27698,29 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>A | 2669呎 (4+房)
-$7877万
-$29,514/呎
-(25年-03月-13日)</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$3125万
-$26,347/呎
-(26年-01月-19日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3612万
-$26,426/呎
-(24年-07月-26日)</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
+$3454万
+$25,264/呎
+(25年-03月-03日)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3618万
-$26,444/呎
-(24年-07月-26日)</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$3002万
-$25,315/呎
-(26年-06月-04日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3500万
-$25,604/呎
-(24年-10月-10日)</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3473万
-$25,386/呎
-(24年-12月-24日)</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="inlineStr">
+$3429万
+$25,069/呎
+(25年-03月-03日)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -27702,29 +27729,60 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3454万
-$25,264/呎
-(25年-03月-03日)</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
+$3432万
+$25,105/呎
+(24年-12月-16日)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3429万
-$25,069/呎
-(25年-03月-03日)</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
+$3742万
+$27,350/呎
+(25年-03月-14日)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$3325万
+$28,034/呎
+(26年-08月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3425万
+$25,052/呎
+(24年-12月-06日)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3734万
+$27,297/呎
+(25年-03月-14日)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -27733,60 +27791,246 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3432万
-$25,105/呎
+$3417万
+$24,999/呎
 (24年-12月-16日)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3742万
-$27,350/呎
-(25年-03月-14日)</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
+$3727万
+$27,244/呎
+(25年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
-$3325万
-$26,578/呎
-(26年-07月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
+$3265万
+$26,098/呎
+(26年-08月-04日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3425万
-$25,052/呎
-(24年-12月-06日)</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
+$3417万
+$24,999/呎
+(24年-12月-10日)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3734万
-$27,297/呎
-(25年-03月-14日)</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
+$3340万
+$24,415/呎
+(25年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2753万
+$23,210/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3396万
+$24,841/呎
+(24年-11月-21日)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3321万
+$24,275/呎
+(25年-07月-22日)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2852万
+$24,050/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3403万
+$24,894/呎
+(24年-12月-24日)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3313万
+$24,218/呎
+(25年-06月-13日)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2830万
+$23,860/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$4198万
+$30,710/呎
+(26年-02月-10日)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3270万
+$23,905/呎
+(25年-08月-07日)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3374万
+$24,682/呎
+(25年-01月-03日)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3227万
+$23,588/呎
+(24年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2792万
+$23,543/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3665万
+$26,811/呎
+(25年-06月-13日)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3270万
+$23,905/呎
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 1186呎 (3房)
+$2815万
+$23,733/呎
+(26年-07月-28日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 1367呎 (3房)
+$3338万
+$24,418/呎
+(25年-11月-20日)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1368呎 (3房)
+$3205万
+$23,429/呎
+(25年-08月-15日)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -27795,153 +28039,29 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3417万
-$24,999/呎
-(24年-12月-16日)</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
+$3330万
+$24,360/呎
+(25年-11月-19日)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3727万
-$27,244/呎
-(25年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-$3265万
-$26,098/呎
-(26年-08月-04日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3417万
-$24,999/呎
-(24年-12月-10日)</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3340万
-$24,415/呎
-(25年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2753万
-$23,210/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3396万
-$24,841/呎
-(24年-11月-21日)</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3321万
-$24,275/呎
-(25年-07月-22日)</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2852万
-$24,050/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3403万
-$24,894/呎
-(24年-12月-24日)</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3313万
-$24,218/呎
-(25年-06月-13日)</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2830万
-$23,860/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$4198万
-$30,710/呎
-(26年-02月-10日)</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3270万
-$23,905/呎
-(25年-08月-07日)</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
+$3212万
+$23,482/呎
+(26年-03月-30日)</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 招标单位
@@ -27950,91 +28070,60 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3374万
-$24,682/呎
-(25年-01月-03日)</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
+$3352万
+$24,524/呎
+(25年-12月-17日)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3227万
-$23,588/呎
-(24年-08月-23日)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2792万
-$23,543/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
+$3209万
+$23,461/呎
+(26年-04月-13日)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+$2740万
+$21,900/呎
+(26年-08月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 1367呎 (3房)
-$3665万
-$26,811/呎
-(25年-06月-13日)</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
+$3324万
+$24,312/呎
+(24年-04月-12日)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 1368呎 (3房)
-$3270万
-$23,905/呎
-(26年-04月-20日)</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>C | 1186呎 (3房)
-$2815万
-$23,733/呎
-(26年-07月-28日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3338万
-$24,418/呎
-(25年-11月-20日)</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3205万
-$23,429/呎
-(25年-08月-15日)</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
+$3193万
+$23,342/呎
+(24年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -28043,99 +28132,6 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3330万
-$24,360/呎
-(25年-11月-19日)</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3212万
-$23,482/呎
-(26年-03月-30日)</t>
-        </is>
-      </c>
-      <c r="D22" s="23" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3352万
-$24,524/呎
-(25年-12月-17日)</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3209万
-$23,461/呎
-(26年-04月-13日)</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
-$2740万
-$21,900/呎
-(26年-08月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>A | 1367呎 (3房)
-$3324万
-$24,312/呎
-(24年-04月-12日)</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>B | 1368呎 (3房)
-$3193万
-$23,342/呎
-(24年-04月-08日)</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
         <is>
@@ -28163,7 +28159,7 @@
           <t>C | 1186呎 (3房)
 $2690万
 $22,678/呎
-(26年-07月-20日)</t>
+(26年-08月-19日)</t>
         </is>
       </c>
     </row>
@@ -29278,12 +29274,30 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 3255呎 (4+房)
+$11039万
+$33,915/呎
+(25年-02月-26日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 845呎 (2房)
 $1984万
@@ -29291,7 +29305,7 @@
 (25年-03月-11日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 845呎 (2房)
 $1873万
@@ -29299,24 +29313,6 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 3255呎 (4+房)
-$11039万
-$33,915/呎
-(25年-02月-26日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30234,27 +30230,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
     </row>
@@ -30389,12 +30385,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>C | 890呎 (2房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -30490,20 +30486,20 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 1399呎 (3房)
+$3204万
+$22,900/呎
+(26年-08月-18日)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 1398呎 (3房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>B | 1398呎 (3房)
--
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -31057,11 +31053,36 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1924万
+$23,811/呎
+(24年-03月-18日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1934万
+$23,931/呎
+(24年-02月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>20&amp;21</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 2905呎 (4+房)
 $9870万
@@ -31069,33 +31090,8 @@
 (26年-04月-13日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1924万
-$23,811/呎
-(24年-03月-18日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1934万
-$23,931/呎
-(24年-02月-02日)</t>
-        </is>
-      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -32041,7 +32037,7 @@
           <t>A | 1321呎 (3房)
 $3082万
 $23,332/呎
-(26年-05月-29日)</t>
+(26年-08月-19日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">

--- a/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
+++ b/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1251</v>
+        <v>1186</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2196,14 +2196,14 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
         <v>32648300</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>26098</v>
+        <v>27528</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         </is>
       </c>
       <c r="E233" s="4" t="n">
-        <v>898</v>
+        <v>811</v>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
@@ -16022,14 +16022,14 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
         <v>20833600</v>
       </c>
       <c r="I233" s="5" t="n">
-        <v>23200</v>
+        <v>25689</v>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
@@ -16079,7 +16079,7 @@
         </is>
       </c>
       <c r="E234" s="4" t="n">
-        <v>890</v>
+        <v>813</v>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
@@ -16088,14 +16088,14 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
         <v>21271000</v>
       </c>
       <c r="I234" s="5" t="n">
-        <v>23900</v>
+        <v>26164</v>
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
@@ -16351,23 +16351,19 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H238" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I238" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H238" s="5" t="n">
+        <v>20915000</v>
+      </c>
+      <c r="I238" s="5" t="n">
+        <v>23500</v>
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
@@ -16376,12 +16372,12 @@
       </c>
       <c r="K238" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M238" s="3" t="inlineStr">
@@ -16391,7 +16387,7 @@
       </c>
       <c r="N238" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -19545,7 +19541,7 @@
         </is>
       </c>
       <c r="E285" s="4" t="n">
-        <v>892</v>
+        <v>812</v>
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
@@ -19554,14 +19550,14 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
         <v>18553600</v>
       </c>
       <c r="I285" s="5" t="n">
-        <v>20800</v>
+        <v>22849</v>
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
@@ -27574,11 +27570,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27&amp;28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 6681呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1442呎 (1房)
 -
@@ -27586,7 +27599,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -27595,23 +27608,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27&amp;28&amp;29</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 6681呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -27815,10 +27811,10 @@
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t>C | 1251呎 (3房)
+          <t>C | 1186呎 (3房)
 $3265万
-$26,098/呎
-(26年-08月-04日)</t>
+$27,528/呎
+(26年-08月-25日)</t>
         </is>
       </c>
     </row>
@@ -29274,10 +29270,35 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1984万
+$23,479/呎
+(25年-03月-11日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 845呎 (2房)
+$1873万
+$22,169/呎
+(25年-07月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 3255呎 (4+房)
 $11039万
@@ -29285,34 +29306,9 @@
 (25年-02月-26日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
       <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1984万
-$23,479/呎
-(25年-03月-11日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 845呎 (2房)
-$1873万
-$22,169/呎
-(25年-07月-11日)</t>
-        </is>
-      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30230,7 +30226,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -30240,7 +30236,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -30316,11 +30312,29 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 2403呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1399呎 (3房)
 $3398万
@@ -30328,40 +30342,22 @@
 (26年-08月-08日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>C | 890呎 (2房)
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
 $2127万
-$23,900/呎
-(26年-08月-03日)</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>D | 898呎 (2房)
+$26,164/呎
+(26年-08月-25日)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 811呎 (2房)
 $2083万
-$23,200/呎
-(26年-08月-04日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 2403呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
+$25,689/呎
+(26年-08月-25日)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30385,12 +30381,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 890呎 (2房)
-招标单位
--
-(在售)</t>
+$2092万
+$23,500/呎
+(26年-08月-24日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -30863,10 +30859,10 @@
       </c>
       <c r="E20" s="21" t="inlineStr">
         <is>
-          <t>D | 892呎 (2房)
+          <t>D | 812呎 (2房)
 $1855万
-$20,800/呎
-(26年-08月-03日)</t>
+$22,849/呎
+(26年-08月-24日)</t>
         </is>
       </c>
     </row>
@@ -31096,11 +31092,29 @@
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 2258呎 (4+房)
+$7128万
+$31,568/呎
+(26年-01月-27日)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr"/>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 1264呎 (3房)
 $3021万
@@ -31108,7 +31122,7 @@
 (25年-10月-08日)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 808呎 (2房)
 $1912万
@@ -31116,7 +31130,7 @@
 (24年-03月-22日)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (2房)
 $1916万
@@ -31124,24 +31138,6 @@
 (24年-01月-12日)</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>A | 2258呎 (4+房)
-$7128万
-$31,568/呎
-(26年-01月-27日)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -31833,11 +31829,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2271呎 (4+房)
+$7508万
+$33,060/呎
+(25年-11月-24日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1352呎 (3房)
 $3628万
@@ -31845,7 +31858,7 @@
 (26年-01月-19日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 785呎 (2房)
 $1849万
@@ -31853,23 +31866,6 @@
 (24年-06月-17日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2271呎 (4+房)
-$7508万
-$33,060/呎
-(25年-11月-24日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
+++ b/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
@@ -25113,7 +25113,7 @@
       </c>
       <c r="F369" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G369" s="3" t="inlineStr">
@@ -25123,12 +25123,12 @@
       </c>
       <c r="H369" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I369" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J369" s="3" t="inlineStr">
@@ -25138,12 +25138,12 @@
       </c>
       <c r="K369" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L369" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M369" s="3" t="inlineStr">
@@ -25153,7 +25153,7 @@
       </c>
       <c r="N369" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -25179,7 +25179,7 @@
         </is>
       </c>
       <c r="E370" s="4" t="n">
-        <v>1401</v>
+        <v>1321</v>
       </c>
       <c r="F370" s="3" t="inlineStr">
         <is>
@@ -25188,14 +25188,14 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
         <v>33343800</v>
       </c>
       <c r="I370" s="5" t="n">
-        <v>23800</v>
+        <v>25241</v>
       </c>
       <c r="J370" s="3" t="inlineStr">
         <is>
@@ -27570,10 +27570,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1442呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 1251呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28&amp;29</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 6681呎 (4+房)
 -
@@ -27581,32 +27605,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>B | 1442呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>C | 1251呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -28420,10 +28420,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1351呎 (3房)
+$3630万
+$26,866/呎
+(24年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2612万
+$22,139/呎
+(25年-09月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2338呎 (4+房)
 $7600万
@@ -28431,32 +28455,8 @@
 (24年-04月-09日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1351呎 (3房)
-$3630万
-$26,866/呎
-(24年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2612万
-$22,139/呎
-(25年-09月-12日)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30312,10 +30312,42 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1399呎 (3房)
+$3398万
+$24,289/呎
+(26年-08月-08日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$2127万
+$26,164/呎
+(26年-08月-25日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 811呎 (2房)
+$2083万
+$25,689/呎
+(26年-08月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19&amp;20</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 2403呎 (4+房)
 -
@@ -30323,41 +30355,9 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1399呎 (3房)
-$3398万
-$24,289/呎
-(26年-08月-08日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$2127万
-$26,164/呎
-(26年-08月-25日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 811呎 (2房)
-$2083万
-$25,689/呎
-(26年-08月-25日)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -31049,12 +31049,30 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>20&amp;21</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 2905呎 (4+房)
+$9870万
+$33,976/呎
+(26年-04月-13日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 808呎 (2房)
 $1924万
@@ -31062,7 +31080,7 @@
 (24年-03月-18日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (2房)
 $1934万
@@ -31071,31 +31089,45 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>20&amp;21</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 2905呎 (4+房)
-$9870万
-$33,976/呎
-(26年-04月-13日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr"/>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 1264呎 (3房)
+$3021万
+$23,902/呎
+(25年-10月-08日)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1912万
+$23,663/呎
+(24年-03月-22日)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1916万
+$23,712/呎
+(24年-01月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
           <t>19&amp;20</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 2258呎 (4+房)
 $7128万
@@ -31103,41 +31135,9 @@
 (26年-01月-27日)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr"/>
-      <c r="D8" s="20" t="inlineStr"/>
-      <c r="E8" s="20" t="inlineStr"/>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>B | 1264呎 (3房)
-$3021万
-$23,902/呎
-(25年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1912万
-$23,663/呎
-(24年-03月-22日)</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1916万
-$23,712/呎
-(24年-01月-12日)</t>
-        </is>
-      </c>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -31756,7 +31756,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -31776,7 +31776,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -31829,10 +31829,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1352呎 (3房)
+$3628万
+$26,833/呎
+(26年-01月-19日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1849万
+$23,558/呎
+(24年-06月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19&amp;20</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2271呎 (4+房)
 $7508万
@@ -31840,32 +31864,8 @@
 (25年-11月-24日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1352呎 (3房)
-$3628万
-$26,833/呎
-(26年-01月-19日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1849万
-$23,558/呎
-(24年-06月-17日)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -31937,18 +31937,18 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>A | 1401呎 (3房)
+          <t>A | 1321呎 (3房)
 $3334万
-$23,800/呎
-(26年-08月-11日)</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
+$25,241/呎
+(26年-08月-28日)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 1415呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">

--- a/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
+++ b/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
@@ -27570,11 +27570,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27&amp;28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 6681呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1442呎 (1房)
 -
@@ -27582,7 +27599,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 1251呎 (3房)
 -
@@ -27590,23 +27607,6 @@
 (待售)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27&amp;28&amp;29</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 6681呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -28420,11 +28420,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2338呎 (4+房)
+$7600万
+$32,506/呎
+(24年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1351呎 (3房)
 $3630万
@@ -28432,7 +28449,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1180呎 (3房)
 $2612万
@@ -28440,23 +28457,6 @@
 (25年-09月-12日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2338呎 (4+房)
-$7600万
-$32,506/呎
-(24年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -29270,12 +29270,30 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 3255呎 (4+房)
+$11039万
+$33,915/呎
+(25年-02月-26日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 845呎 (2房)
 $1984万
@@ -29283,7 +29301,7 @@
 (25年-03月-11日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 845呎 (2房)
 $1873万
@@ -29291,24 +29309,6 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 3255呎 (4+房)
-$11039万
-$33,915/呎
-(25年-02月-26日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -31049,11 +31049,36 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 808呎 (2房)
+$1924万
+$23,811/呎
+(24年-03月-18日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 808呎 (2房)
+$1934万
+$23,931/呎
+(24年-02月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>20&amp;21</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 2905呎 (4+房)
 $9870万
@@ -31061,33 +31086,8 @@
 (26年-04月-13日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 808呎 (2房)
-$1924万
-$23,811/呎
-(24年-03月-18日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 808呎 (2房)
-$1934万
-$23,931/呎
-(24年-02月-02日)</t>
-        </is>
-      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
+++ b/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
@@ -16145,7 +16145,7 @@
         </is>
       </c>
       <c r="E235" s="4" t="n">
-        <v>1399</v>
+        <v>1287</v>
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
@@ -16154,14 +16154,14 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
         <v>33980000</v>
       </c>
       <c r="I235" s="5" t="n">
-        <v>24289</v>
+        <v>26402</v>
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
@@ -25113,23 +25113,19 @@
       </c>
       <c r="F369" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H369" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I369" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H369" s="5" t="n">
+        <v>33252500</v>
+      </c>
+      <c r="I369" s="5" t="n">
+        <v>23500</v>
       </c>
       <c r="J369" s="3" t="inlineStr">
         <is>
@@ -25138,12 +25134,12 @@
       </c>
       <c r="K369" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L369" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M369" s="3" t="inlineStr">
@@ -25153,7 +25149,7 @@
       </c>
       <c r="N369" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -25513,23 +25509,19 @@
       </c>
       <c r="F375" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H375" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I375" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H375" s="5" t="n">
+        <v>36400000</v>
+      </c>
+      <c r="I375" s="5" t="n">
+        <v>25724</v>
       </c>
       <c r="J375" s="3" t="inlineStr">
         <is>
@@ -25538,12 +25530,12 @@
       </c>
       <c r="K375" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L375" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M375" s="3" t="inlineStr">
@@ -25553,7 +25545,7 @@
       </c>
       <c r="N375" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -25715,23 +25707,19 @@
       </c>
       <c r="F378" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H378" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I378" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H378" s="5" t="n">
+        <v>32318600</v>
+      </c>
+      <c r="I378" s="5" t="n">
+        <v>22840</v>
       </c>
       <c r="J378" s="3" t="inlineStr">
         <is>
@@ -25740,12 +25728,12 @@
       </c>
       <c r="K378" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L378" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M378" s="3" t="inlineStr">
@@ -25755,7 +25743,7 @@
       </c>
       <c r="N378" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -26713,23 +26701,19 @@
       </c>
       <c r="F393" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H393" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I393" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H393" s="5" t="n">
+        <v>31059250</v>
+      </c>
+      <c r="I393" s="5" t="n">
+        <v>21950</v>
       </c>
       <c r="J393" s="3" t="inlineStr">
         <is>
@@ -26738,12 +26722,12 @@
       </c>
       <c r="K393" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L393" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M393" s="3" t="inlineStr">
@@ -26753,7 +26737,7 @@
       </c>
       <c r="N393" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -28420,10 +28404,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1351呎 (3房)
+$3630万
+$26,866/呎
+(24年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1180呎 (3房)
+$2612万
+$22,139/呎
+(25年-09月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2338呎 (4+房)
 $7600万
@@ -28431,32 +28439,8 @@
 (24年-04月-09日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1351呎 (3房)
-$3630万
-$26,866/呎
-(24年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1180呎 (3房)
-$2612万
-$22,139/呎
-(25年-09月-12日)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -29270,10 +29254,35 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 845呎 (2房)
+$1984万
+$23,479/呎
+(25年-03月-11日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 845呎 (2房)
+$1873万
+$22,169/呎
+(25年-07月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 3255呎 (4+房)
 $11039万
@@ -29281,34 +29290,9 @@
 (25年-02月-26日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
       <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 845呎 (2房)
-$1984万
-$23,479/呎
-(25年-03月-11日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 845呎 (2房)
-$1873万
-$22,169/呎
-(25年-07月-11日)</t>
-        </is>
-      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30312,19 +30296,37 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 2403呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 1399呎 (3房)
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 1287呎 (3房)
 $3398万
-$24,289/呎
-(26年-08月-08日)</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
+$26,402/呎
+(26年-09月-02日)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 813呎 (2房)
 $2127万
@@ -30332,7 +30334,7 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 811呎 (2房)
 $2083万
@@ -30340,24 +30342,6 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 2403呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -31756,7 +31740,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -31766,7 +31750,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>41</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -31829,11 +31813,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2271呎 (4+房)
+$7508万
+$33,060/呎
+(25年-11月-24日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1352呎 (3房)
 $3628万
@@ -31841,7 +31842,7 @@
 (26年-01月-19日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 785呎 (2房)
 $1849万
@@ -31850,23 +31851,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2271呎 (4+房)
-$7508万
-$33,060/呎
-(25年-11月-24日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -31943,7 +31927,131 @@
 (26年-08月-28日)</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 1415呎 (3房)
+$3325万
+$23,500/呎
+(26年-09月-01日)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1778万
+$22,644/呎
+(24年-04月-18日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 1321呎 (3房)
+$3115万
+$23,584/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 1340呎 (3房)
+$3136万
+$23,400/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1754万
+$22,340/呎
+(24年-04月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 1321呎 (3房)
+$3110万
+$23,544/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 1415呎 (3房)
+$3640万
+$25,724/呎
+(26年-09月-01日)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1618万
+$20,611/呎
+(25年-12月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 1321呎 (3房)
+$3082万
+$23,332/呎
+(26年-08月-19日)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 1415呎 (3房)
+$3232万
+$22,840/呎
+(26年-09月-01日)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1598万
+$20,357/呎
+(26年-02月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 1321呎 (3房)
+$3050万
+$23,089/呎
+(26年-05月-28日)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 1415呎 (3房)
 招标单位
@@ -31951,130 +32059,6 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1778万
-$22,644/呎
-(24年-04月-18日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>A | 1321呎 (3房)
-$3115万
-$23,584/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>B | 1340呎 (3房)
-$3136万
-$23,400/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1754万
-$22,340/呎
-(24年-04月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>A | 1321呎 (3房)
-$3110万
-$23,544/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>B | 1415呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1618万
-$20,611/呎
-(25年-12月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>A | 1321呎 (3房)
-$3082万
-$23,332/呎
-(26年-08月-19日)</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>B | 1415呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1598万
-$20,357/呎
-(26年-02月-11日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>A | 1321呎 (3房)
-$3050万
-$23,089/呎
-(26年-05月-28日)</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>B | 1415呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 785呎 (2房)
@@ -32191,12 +32175,12 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 1415呎 (3房)
-招标单位
--
-(在售)</t>
+$3106万
+$21,950/呎
+(26年-09月-01日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">

--- a/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
+++ b/九龙-何文田-傲玟/傲玟_销控明细表.xlsx
@@ -17299,7 +17299,7 @@
         </is>
       </c>
       <c r="E252" s="4" t="n">
-        <v>1399</v>
+        <v>1278</v>
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>32037100</v>
       </c>
       <c r="I252" s="5" t="n">
-        <v>22900</v>
+        <v>25068</v>
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
@@ -28404,11 +28404,28 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2338呎 (4+房)
+$7600万
+$32,506/呎
+(24年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1351呎 (3房)
 $3630万
@@ -28416,7 +28433,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1180呎 (3房)
 $2612万
@@ -28424,23 +28441,6 @@
 (25年-09月-12日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2338呎 (4+房)
-$7600万
-$32,506/呎
-(24年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -29254,12 +29254,30 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 3255呎 (4+房)
+$11039万
+$33,915/呎
+(25年-02月-26日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 845呎 (2房)
 $1984万
@@ -29267,7 +29285,7 @@
 (25年-03月-11日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 845呎 (2房)
 $1873万
@@ -29275,24 +29293,6 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 3255呎 (4+房)
-$11039万
-$33,915/呎
-(25年-02月-26日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30296,10 +30296,42 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1287呎 (3房)
+$3398万
+$26,402/呎
+(26年-09月-02日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 813呎 (2房)
+$2127万
+$26,164/呎
+(26年-08月-25日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 811呎 (2房)
+$2083万
+$25,689/呎
+(26年-08月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19&amp;20</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 2403呎 (4+房)
 -
@@ -30307,41 +30339,9 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1287呎 (3房)
-$3398万
-$26,402/呎
-(26年-09月-02日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 813呎 (2房)
-$2127万
-$26,164/呎
-(26年-08月-25日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 811呎 (2房)
-$2083万
-$25,689/呎
-(26年-08月-25日)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30468,9 +30468,9 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 1399呎 (3房)
+          <t>A | 1278呎 (3房)
 $3204万
-$22,900/呎
+$25,068/呎
 (26年-08月-18日)</t>
         </is>
       </c>
@@ -31076,11 +31076,29 @@
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 2258呎 (4+房)
+$7128万
+$31,568/呎
+(26年-01月-27日)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr"/>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 1264呎 (3房)
 $3021万
@@ -31088,7 +31106,7 @@
 (25年-10月-08日)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 808呎 (2房)
 $1912万
@@ -31096,7 +31114,7 @@
 (24年-03月-22日)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (2房)
 $1916万
@@ -31104,24 +31122,6 @@
 (24年-01月-12日)</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>19&amp;20</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>A | 2258呎 (4+房)
-$7128万
-$31,568/呎
-(26年-01月-27日)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -31813,10 +31813,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1352呎 (3房)
+$3628万
+$26,833/呎
+(26年-01月-19日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 785呎 (2房)
+$1849万
+$23,558/呎
+(24年-06月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>19&amp;20</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2271呎 (4+房)
 $7508万
@@ -31824,32 +31848,8 @@
 (25年-11月-24日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1352呎 (3房)
-$3628万
-$26,833/呎
-(26年-01月-19日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 785呎 (2房)
-$1849万
-$23,558/呎
-(24年-06月-17日)</t>
-        </is>
-      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
